--- a/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
+++ b/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
@@ -579,61 +579,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -881,7 +881,7 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -932,7 +932,7 @@
     <xf numFmtId="164" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -959,7 +959,7 @@
     <xf numFmtId="164" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -980,16 +980,13 @@
     <xf numFmtId="4" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1016,7 +1013,7 @@
     <xf numFmtId="164" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1051,6 +1048,9 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1077,15 +1077,6 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="33" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1111,7 +1102,7 @@
     <xf numFmtId="4" fontId="33" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1126,23 +1117,17 @@
     <xf numFmtId="0" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="30" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="30" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1195,17 +1180,14 @@
     <xf numFmtId="0" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="30" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="30" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2109,132 +2091,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>42</v>
+      <c r="B3" s="244" t="n">
+        <v>43.54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>14.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>3.82</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>5.2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>26.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>تراكم بقوة</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2261,78 +2243,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>63000</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>67000</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>71800</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>75893</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>11100</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>12200</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>13300</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>24689</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>18000</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>20000</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>22000</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>24500</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: البنية الرقمية الوطنية + 5G + STC Pay + حلول سحابة للقطاع الحكومي</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: CAPEX مرتفع · ملكية حكومية قد تؤثر على قرارات التوزيع · منافسة موبايلي/زين</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ ربح 2024 (24.7B) يشمل بيع TAWAL (13.97B غير متكرر) → الربح الجاري ≈ 10.7B ريال</t>
         </is>
@@ -2375,132 +2357,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>185</v>
+      <c r="B3" s="244" t="n">
+        <v>164.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>6.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>30.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>مراقبة / تراكم تدريجي</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2527,78 +2509,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>900</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>1100</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>1452</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>1630</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>320</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>450</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>511</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>661</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>400</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>550</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>680</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>820</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: مطار الملك سلمان الدولي + نمو الشحن الجوي + خدمات الخطوط السعودية</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: تركيز عملاء عالٍ · IPO تقييم مرتفع · بيانات تاريخية قصيرة · تذبذب الأسعار</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: IPO حديث (2022) - بيانات تاريخية محدودة | ✅ إيرادات 2024: 1.63B ريال (تحقق)</t>
         </is>
@@ -2641,132 +2623,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>67</v>
+      <c r="B3" s="244" t="n">
+        <v>59.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>20.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>3.35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>17.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>احتفاظ / تراكم عند الضعف</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2793,78 +2775,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>2050</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>2400</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>2706</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>2879</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>520</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>680</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>658</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>646</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>650</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>820</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>800</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>780</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: خصخصة الصحة + التأمين الإلزامي + السياحة الطبية + توسع في المدينة</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: تراجع هامش الربح · شح الكوادر الطبية · تنافسية القطاع الخاص المتنامية</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: توزيع سنوي ثابت منذ الإدراج</t>
         </is>
@@ -2907,132 +2889,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>38</v>
+      <c r="B3" s="244" t="n">
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>12.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>17.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>متوسط-مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>مراقبة - انتظار توضيح Q1 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3059,78 +3041,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>1200</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>1500</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>1750</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>1980</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>185</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>240</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>277</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>380</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>460</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>510</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>550</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: السياحة + الفعاليات والترفيه + تأجير أسطول NEOM + نمو المطارات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: ⚠ تراجع ربح Q1 2026 بـ58% · رأس مال مكثف للأسطول · منافسة منصات المشاركة</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ انخفاض أرباح Q1 2026 بنسبة 58% - يستوجب مراقبة</t>
         </is>
@@ -3173,132 +3155,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>95</v>
+      <c r="B3" s="244" t="n">
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>14.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>5.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>30.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3325,78 +3307,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>4500</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>5200</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>5800</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>6781</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>280</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>340</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>390</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>534</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>350</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>430</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: نمو الإنفاق الاستهلاكي + التحول الرقمي + تراخيص جديدة + توسع جغرافي</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: منافسة أمازون.sa ونون · ضغط هوامش التجزئة · التحدي الرقمي</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ✅ توزيع استثنائي أغسطس 2024: 5 ريال/سهم من الاحتياطيات | ربح FY2024: 534.5M ريال</t>
         </is>
@@ -3439,128 +3421,128 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>48</v>
+      <c r="B3" s="244" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n"/>
+      <c r="B6" s="246" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n"/>
+      <c r="B9" s="244" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>مضاربة / وزن محدود</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3587,78 +3569,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>2100</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>2400</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>1900</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>1700</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>380</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>320</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>85</v>
       </c>
-      <c r="E17" s="260" t="n">
+      <c r="E17" s="254" t="n">
         <v>-259</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>450</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>380</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>180</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تحويل البلاستيك للمواد الإنشائية (NEOM) + طاقة انتاجية جديدة + تنويع المنتجات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: ⚠ دورية البتروكيماويات · خسارة 2024 · أسعار البروبيلين العالمية · منافسة صينية</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ لا توزيعات 2023-2024 بسبب الخسارة | العودة للربحية Q1 2025</t>
         </is>
@@ -3701,132 +3683,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>10.2</v>
+      <c r="B3" s="244" t="n">
+        <v>9.25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>1630</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>14.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>1.03</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>7.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>احتفاظ للدخل</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3853,78 +3835,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>140</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>155</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>170</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>190</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>85</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>95</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>105</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>90</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>115</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: نمو القطاع العقاري + الطلب السياحي + نمو الإيجارات التجارية</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: حساسية أسعار الفائدة · جودة المستأجرين · إعادة التقييم العقاري · تركيز الأصول</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: توزيع نصف سنوي إلزامي ≥90% من الدخل الصافي</t>
         </is>
@@ -4083,7 +4065,7 @@
         </is>
       </c>
       <c r="E4" s="25" t="n">
-        <v>69.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F4" s="26" t="n">
         <v>14</v>
@@ -4139,7 +4121,7 @@
         </is>
       </c>
       <c r="E5" s="31" t="n">
-        <v>27.5</v>
+        <v>23.53</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>9.4</v>
@@ -4195,7 +4177,7 @@
         </is>
       </c>
       <c r="E6" s="25" t="n">
-        <v>42</v>
+        <v>43.54</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>14.2</v>
@@ -4251,7 +4233,7 @@
         </is>
       </c>
       <c r="E7" s="31" t="n">
-        <v>185</v>
+        <v>164.1</v>
       </c>
       <c r="F7" s="32" t="n">
         <v>22.4</v>
@@ -4307,7 +4289,7 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>67</v>
+        <v>59.1</v>
       </c>
       <c r="F8" s="39" t="n">
         <v>20.7</v>
@@ -4363,7 +4345,7 @@
         </is>
       </c>
       <c r="E9" s="31" t="n">
-        <v>38</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F9" s="32" t="n">
         <v>12.2</v>
@@ -4419,7 +4401,7 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>95</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F10" s="39" t="n">
         <v>14.4</v>
@@ -4475,7 +4457,7 @@
         </is>
       </c>
       <c r="E11" s="25" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
@@ -4537,7 +4519,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>10.2</v>
+        <v>9.25</v>
       </c>
       <c r="F12" s="39" t="n">
         <v>14.1</v>
@@ -4616,7 +4598,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  الراجحي (1120) — مصرفي  ⚠ منح سهم لكل سهمين في H2 2025 → سترتفع الأسهم إلى 6,000M</t>
+          <t xml:space="preserve">  الراجحي (1120) — مصرفي  ✅ سعر مُعدَّل بعد المنح (1 سهم / 2) → الأسهم ارتفعت من 4B إلى 6B</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9025,7 @@
         </is>
       </c>
       <c r="B4" s="83" t="n">
-        <v>69.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C4" s="84" t="n">
         <v>14</v>
@@ -9058,7 +9040,7 @@
         <v>1.46</v>
       </c>
       <c r="G4" s="85" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="H4" s="88" t="n">
         <v>83</v>
@@ -9082,7 +9064,7 @@
       </c>
       <c r="N4" s="91" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+11.4%</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9075,7 @@
         </is>
       </c>
       <c r="B5" s="93" t="n">
-        <v>27.5</v>
+        <v>23.53</v>
       </c>
       <c r="C5" s="94" t="n">
         <v>9.4</v>
@@ -9108,7 +9090,7 @@
         <v>0.32</v>
       </c>
       <c r="G5" s="95" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="H5" s="98" t="n">
         <v>35</v>
@@ -9132,7 +9114,7 @@
       </c>
       <c r="N5" s="101" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+22.4%</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9125,7 @@
         </is>
       </c>
       <c r="B6" s="103" t="n">
-        <v>42</v>
+        <v>43.54</v>
       </c>
       <c r="C6" s="104" t="n">
         <v>14.2</v>
@@ -9158,7 +9140,7 @@
         <v>0.47</v>
       </c>
       <c r="G6" s="105" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H6" s="108" t="n">
         <v>51</v>
@@ -9180,7 +9162,7 @@
       </c>
       <c r="N6" s="109" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+12.8%</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9173,7 @@
         </is>
       </c>
       <c r="B7" s="111" t="n">
-        <v>185</v>
+        <v>164.1</v>
       </c>
       <c r="C7" s="112" t="n">
         <v>22.4</v>
@@ -9206,7 +9188,7 @@
         <v>0.82</v>
       </c>
       <c r="G7" s="113" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="H7" s="116" t="n">
         <v>220</v>
@@ -9223,12 +9205,12 @@
       <c r="L7" s="117" t="n">
         <v>137.8</v>
       </c>
-      <c r="M7" s="117" t="n">
+      <c r="M7" s="116" t="n">
         <v>178.4</v>
       </c>
       <c r="N7" s="118" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+10.4%</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9221,7 @@
         </is>
       </c>
       <c r="B8" s="120" t="n">
-        <v>67</v>
+        <v>59.1</v>
       </c>
       <c r="C8" s="121" t="n">
         <v>20.7</v>
@@ -9254,7 +9236,7 @@
         <v>2.76</v>
       </c>
       <c r="G8" s="122" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H8" s="125" t="n">
         <v>74</v>
@@ -9268,7 +9250,7 @@
       <c r="K8" s="126" t="n">
         <v>52.1</v>
       </c>
-      <c r="L8" s="126" t="n">
+      <c r="L8" s="125" t="n">
         <v>61.2</v>
       </c>
       <c r="M8" s="125" t="n">
@@ -9276,7 +9258,7 @@
       </c>
       <c r="N8" s="127" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+14.2%</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9269,7 @@
         </is>
       </c>
       <c r="B9" s="129" t="n">
-        <v>38</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C9" s="130" t="n">
         <v>12.2</v>
@@ -9302,12 +9284,12 @@
         <v>0.64</v>
       </c>
       <c r="G9" s="131" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="H9" s="134" t="n">
         <v>46</v>
       </c>
-      <c r="I9" s="135" t="n">
+      <c r="I9" s="134" t="n">
         <v>38</v>
       </c>
       <c r="J9" s="134" t="n">
@@ -9319,12 +9301,12 @@
       <c r="L9" s="134" t="n">
         <v>49.3</v>
       </c>
-      <c r="M9" s="134" t="n">
+      <c r="M9" s="135" t="n">
         <v>90.2</v>
       </c>
       <c r="N9" s="136" t="inlineStr">
         <is>
-          <t>+16.1%</t>
+          <t>-41.9%</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9317,7 @@
         </is>
       </c>
       <c r="B10" s="111" t="n">
-        <v>95</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="C10" s="112" t="n">
         <v>14.4</v>
@@ -9350,7 +9332,7 @@
         <v>0.6</v>
       </c>
       <c r="G10" s="113" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H10" s="116" t="n">
         <v>115</v>
@@ -9364,128 +9346,128 @@
       <c r="K10" s="116" t="n">
         <v>106.2</v>
       </c>
-      <c r="L10" s="117" t="n">
+      <c r="L10" s="116" t="n">
         <v>86.8</v>
       </c>
       <c r="M10" s="116" t="n">
         <v>111.7</v>
       </c>
-      <c r="N10" s="137" t="inlineStr">
-        <is>
-          <t>+7.6%</t>
+      <c r="N10" s="118" t="inlineStr">
+        <is>
+          <t>+24.8%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="138" t="inlineStr">
+      <c r="A11" s="137" t="inlineStr">
         <is>
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B11" s="139" t="n">
-        <v>48</v>
-      </c>
-      <c r="C11" s="140" t="inlineStr">
+      <c r="B11" s="138" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" s="139" t="inlineStr">
         <is>
           <t>خسارة</t>
         </is>
       </c>
-      <c r="D11" s="141" t="n">
+      <c r="D11" s="140" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="142" t="n">
+      <c r="E11" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="143" t="inlineStr">
+      <c r="F11" s="142" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="141" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H11" s="144" t="n">
+      <c r="G11" s="140" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" s="143" t="n">
         <v>60</v>
       </c>
-      <c r="I11" s="143" t="inlineStr">
+      <c r="I11" s="142" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="144" t="n">
+      <c r="J11" s="143" t="n">
         <v>55</v>
       </c>
-      <c r="K11" s="143" t="inlineStr">
+      <c r="K11" s="142" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="145" t="n">
+      <c r="L11" s="144" t="n">
         <v>3.6</v>
       </c>
-      <c r="M11" s="145" t="n">
+      <c r="M11" s="143" t="n">
         <v>38.8</v>
       </c>
-      <c r="N11" s="146" t="inlineStr">
-        <is>
-          <t>-17.7%</t>
+      <c r="N11" s="145" t="inlineStr">
+        <is>
+          <t>+31.7%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="147" t="inlineStr">
+      <c r="A12" s="146" t="inlineStr">
         <is>
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B12" s="148" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="C12" s="149" t="n">
+      <c r="B12" s="147" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="C12" s="148" t="n">
         <v>14.1</v>
       </c>
-      <c r="D12" s="150" t="n">
+      <c r="D12" s="149" t="n">
         <v>1.03</v>
       </c>
-      <c r="E12" s="151" t="n">
+      <c r="E12" s="150" t="n">
         <v>7.5</v>
       </c>
-      <c r="F12" s="152" t="n">
+      <c r="F12" s="151" t="n">
         <v>1.22</v>
       </c>
-      <c r="G12" s="150" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H12" s="153" t="n">
+      <c r="G12" s="149" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H12" s="152" t="n">
         <v>10.8</v>
       </c>
-      <c r="I12" s="153" t="n">
+      <c r="I12" s="152" t="n">
         <v>11.5</v>
       </c>
-      <c r="J12" s="153" t="n">
+      <c r="J12" s="152" t="n">
         <v>10.5</v>
       </c>
-      <c r="K12" s="153" t="n">
+      <c r="K12" s="152" t="n">
         <v>14.8</v>
       </c>
-      <c r="L12" s="154" t="inlineStr">
+      <c r="L12" s="153" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" s="154" t="inlineStr">
+      <c r="M12" s="153" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N12" s="155" t="inlineStr">
-        <is>
-          <t>+16.7%</t>
+      <c r="N12" s="154" t="inlineStr">
+        <is>
+          <t>+28.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="156" t="inlineStr">
+      <c r="A14" s="155" t="inlineStr">
         <is>
           <t>منهجية: P/E = متوسط P/E قطاعي × EPS 2024  |  P/B = متوسط P/B قطاعي × القيمة الدفترية  |  DDM = DPS₁/(WACC−g)  |  DCF = Σ FCF/(1+WACC)^t + Terminal (5 سنوات، g_terminal=3%)  |  EV/EBITDA = EBITDA × Benchmark القطاعي ÷ الأسهم  |  PEG = P/E ÷ CAGR%  |  هامش الأمان = (متوسط 5 طرق − السعر) ÷ السعر  |  ⚠ DCF وEV/EBITDA تقديرات مبنية على OCF كـProxy — راجع ورقة منهجية التقييم للتفاصيل</t>
         </is>
@@ -9527,46 +9509,46 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="157" t="inlineStr">
+      <c r="A2" s="156" t="inlineStr">
         <is>
           <t>⚠ ملاحظة: أسعار بيوت الخبرة المسماة محدودة الإتاحة للعموم — البيانات المُتحقق منها تعتمد على إجماع Investing.com/Bloomberg. | ⚠ أهداف بدجت مُحتسبة قبل نتائج Q1 2026 المخيبة للآمال.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="157" t="inlineStr">
         <is>
           <t>الشركة</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="157" t="inlineStr">
         <is>
           <t>الرمز</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="157" t="inlineStr">
         <is>
           <t>السعر الحالي
 (ريال)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="157" t="inlineStr">
         <is>
           <t>بيت الخبرة / المصدر</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="157" t="inlineStr">
         <is>
           <t>السعر المستهدف
 (ريال)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="157" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="157" t="inlineStr">
         <is>
           <t>Upside%</t>
         </is>
@@ -9584,7 +9566,7 @@
         </is>
       </c>
       <c r="C4" s="160" t="n">
-        <v>69.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D4" s="161" t="inlineStr">
         <is>
@@ -9601,7 +9583,7 @@
       </c>
       <c r="G4" s="164" t="inlineStr">
         <is>
-          <t>+47.6%</t>
+          <t>+53.2%</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9606,7 @@
       </c>
       <c r="G5" s="164" t="inlineStr">
         <is>
-          <t>+36.8%</t>
+          <t>+41.9%</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9629,7 @@
       </c>
       <c r="G6" s="164" t="inlineStr">
         <is>
-          <t>+64.3%</t>
+          <t>+70.4%</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9652,7 @@
       </c>
       <c r="G7" s="164" t="inlineStr">
         <is>
-          <t>+82.3%</t>
+          <t>+89.2%</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9675,7 @@
       </c>
       <c r="G8" s="164" t="inlineStr">
         <is>
-          <t>+43.8%</t>
+          <t>+49.2%</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9698,7 @@
         </is>
       </c>
       <c r="C10" s="160" t="n">
-        <v>27.5</v>
+        <v>23.53</v>
       </c>
       <c r="D10" s="161" t="inlineStr">
         <is>
@@ -9731,9 +9713,9 @@
           <t>شراء (Buy)</t>
         </is>
       </c>
-      <c r="G10" s="167" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
+      <c r="G10" s="164" t="inlineStr">
+        <is>
+          <t>+17.3%</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9738,7 @@
       </c>
       <c r="G11" s="164" t="inlineStr">
         <is>
-          <t>+49.1%</t>
+          <t>+74.2%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9751,7 @@
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E12" s="168" t="n">
+      <c r="E12" s="162" t="n">
         <v>25</v>
       </c>
       <c r="F12" s="163" t="inlineStr">
@@ -9777,9 +9759,9 @@
           <t>محايد</t>
         </is>
       </c>
-      <c r="G12" s="169" t="inlineStr">
-        <is>
-          <t>-9.1%</t>
+      <c r="G12" s="164" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
         </is>
       </c>
     </row>
@@ -9791,81 +9773,81 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="170" t="inlineStr">
+      <c r="A14" s="167" t="inlineStr">
         <is>
           <t>STC</t>
         </is>
       </c>
-      <c r="B14" s="171" t="inlineStr">
+      <c r="B14" s="168" t="inlineStr">
         <is>
           <t>7010</t>
         </is>
       </c>
-      <c r="C14" s="172" t="n">
-        <v>42</v>
-      </c>
-      <c r="D14" s="173" t="inlineStr">
+      <c r="C14" s="169" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="D14" s="170" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E14" s="174" t="n">
+      <c r="E14" s="171" t="n">
         <v>47.7</v>
       </c>
-      <c r="F14" s="175" t="inlineStr">
+      <c r="F14" s="172" t="inlineStr">
         <is>
           <t>شراء (Buy)</t>
         </is>
       </c>
-      <c r="G14" s="176" t="inlineStr">
-        <is>
-          <t>+13.6%</t>
+      <c r="G14" s="173" t="inlineStr">
+        <is>
+          <t>+9.6%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="177" t="inlineStr"/>
-      <c r="B15" s="177" t="inlineStr"/>
-      <c r="C15" s="177" t="inlineStr"/>
-      <c r="D15" s="173" t="inlineStr">
+      <c r="A15" s="174" t="inlineStr"/>
+      <c r="B15" s="174" t="inlineStr"/>
+      <c r="C15" s="174" t="inlineStr"/>
+      <c r="D15" s="170" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E15" s="174" t="n">
+      <c r="E15" s="171" t="n">
         <v>55</v>
       </c>
-      <c r="F15" s="175" t="inlineStr">
+      <c r="F15" s="172" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G15" s="176" t="inlineStr">
-        <is>
-          <t>+31.0%</t>
+      <c r="G15" s="173" t="inlineStr">
+        <is>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="177" t="inlineStr"/>
-      <c r="B16" s="177" t="inlineStr"/>
-      <c r="C16" s="177" t="inlineStr"/>
-      <c r="D16" s="173" t="inlineStr">
+      <c r="A16" s="174" t="inlineStr"/>
+      <c r="B16" s="174" t="inlineStr"/>
+      <c r="C16" s="174" t="inlineStr"/>
+      <c r="D16" s="170" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E16" s="178" t="n">
+      <c r="E16" s="175" t="n">
         <v>41.1</v>
       </c>
-      <c r="F16" s="175" t="inlineStr">
+      <c r="F16" s="172" t="inlineStr">
         <is>
           <t>محايد</t>
         </is>
       </c>
-      <c r="G16" s="179" t="inlineStr">
-        <is>
-          <t>-2.1%</t>
+      <c r="G16" s="176" t="inlineStr">
+        <is>
+          <t>-5.6%</t>
         </is>
       </c>
     </row>
@@ -9877,81 +9859,81 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="180" t="inlineStr">
+      <c r="A18" s="177" t="inlineStr">
         <is>
           <t>سال</t>
         </is>
       </c>
-      <c r="B18" s="181" t="inlineStr">
+      <c r="B18" s="178" t="inlineStr">
         <is>
           <t>4263</t>
         </is>
       </c>
-      <c r="C18" s="182" t="n">
-        <v>185</v>
-      </c>
-      <c r="D18" s="183" t="inlineStr">
+      <c r="C18" s="179" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="D18" s="180" t="inlineStr">
         <is>
           <t>إجماع المحللين</t>
         </is>
       </c>
-      <c r="E18" s="184" t="n">
+      <c r="E18" s="181" t="n">
         <v>178.4</v>
       </c>
-      <c r="F18" s="185" t="inlineStr">
+      <c r="F18" s="182" t="inlineStr">
         <is>
           <t>محايد (Neutral)</t>
         </is>
       </c>
-      <c r="G18" s="186" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
+      <c r="G18" s="183" t="inlineStr">
+        <is>
+          <t>+8.7%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="187" t="inlineStr"/>
-      <c r="B19" s="187" t="inlineStr"/>
-      <c r="C19" s="187" t="inlineStr"/>
-      <c r="D19" s="183" t="inlineStr">
+      <c r="A19" s="184" t="inlineStr"/>
+      <c r="B19" s="184" t="inlineStr"/>
+      <c r="C19" s="184" t="inlineStr"/>
+      <c r="D19" s="180" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E19" s="188" t="n">
+      <c r="E19" s="181" t="n">
         <v>196.1</v>
       </c>
-      <c r="F19" s="185" t="inlineStr">
+      <c r="F19" s="182" t="inlineStr">
         <is>
           <t>شراء</t>
         </is>
       </c>
-      <c r="G19" s="189" t="inlineStr">
-        <is>
-          <t>+6.0%</t>
+      <c r="G19" s="183" t="inlineStr">
+        <is>
+          <t>+19.5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="187" t="inlineStr"/>
-      <c r="B20" s="187" t="inlineStr"/>
-      <c r="C20" s="187" t="inlineStr"/>
-      <c r="D20" s="183" t="inlineStr">
+      <c r="A20" s="184" t="inlineStr"/>
+      <c r="B20" s="184" t="inlineStr"/>
+      <c r="C20" s="184" t="inlineStr"/>
+      <c r="D20" s="180" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E20" s="184" t="n">
+      <c r="E20" s="181" t="n">
         <v>165</v>
       </c>
-      <c r="F20" s="185" t="inlineStr">
+      <c r="F20" s="182" t="inlineStr">
         <is>
           <t>محايد</t>
         </is>
       </c>
-      <c r="G20" s="190" t="inlineStr">
-        <is>
-          <t>-10.8%</t>
+      <c r="G20" s="185" t="inlineStr">
+        <is>
+          <t>+0.5%</t>
         </is>
       </c>
     </row>
@@ -9963,81 +9945,81 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="191" t="inlineStr">
+      <c r="A22" s="186" t="inlineStr">
         <is>
           <t>المواساة</t>
         </is>
       </c>
-      <c r="B22" s="192" t="inlineStr">
+      <c r="B22" s="187" t="inlineStr">
         <is>
           <t>4002</t>
         </is>
       </c>
-      <c r="C22" s="193" t="n">
-        <v>67</v>
-      </c>
-      <c r="D22" s="194" t="inlineStr">
+      <c r="C22" s="188" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="D22" s="189" t="inlineStr">
         <is>
           <t>إجماع (5+ محللين)</t>
         </is>
       </c>
-      <c r="E22" s="195" t="n">
+      <c r="E22" s="190" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="F22" s="196" t="inlineStr">
+      <c r="F22" s="191" t="inlineStr">
         <is>
           <t>شراء (Buy)</t>
         </is>
       </c>
-      <c r="G22" s="197" t="inlineStr">
-        <is>
-          <t>+36.7%</t>
+      <c r="G22" s="192" t="inlineStr">
+        <is>
+          <t>+55.0%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="198" t="inlineStr"/>
-      <c r="B23" s="198" t="inlineStr"/>
-      <c r="C23" s="198" t="inlineStr"/>
-      <c r="D23" s="194" t="inlineStr">
+      <c r="A23" s="193" t="inlineStr"/>
+      <c r="B23" s="193" t="inlineStr"/>
+      <c r="C23" s="193" t="inlineStr"/>
+      <c r="D23" s="189" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E23" s="195" t="n">
+      <c r="E23" s="190" t="n">
         <v>125</v>
       </c>
-      <c r="F23" s="196" t="inlineStr">
+      <c r="F23" s="191" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G23" s="197" t="inlineStr">
-        <is>
-          <t>+86.6%</t>
+      <c r="G23" s="192" t="inlineStr">
+        <is>
+          <t>+111.5%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="198" t="inlineStr"/>
-      <c r="B24" s="198" t="inlineStr"/>
-      <c r="C24" s="198" t="inlineStr"/>
-      <c r="D24" s="194" t="inlineStr">
+      <c r="A24" s="193" t="inlineStr"/>
+      <c r="B24" s="193" t="inlineStr"/>
+      <c r="C24" s="193" t="inlineStr"/>
+      <c r="D24" s="189" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E24" s="195" t="n">
+      <c r="E24" s="190" t="n">
         <v>75.5</v>
       </c>
-      <c r="F24" s="196" t="inlineStr">
+      <c r="F24" s="191" t="inlineStr">
         <is>
           <t>محايد</t>
         </is>
       </c>
-      <c r="G24" s="197" t="inlineStr">
-        <is>
-          <t>+12.7%</t>
+      <c r="G24" s="192" t="inlineStr">
+        <is>
+          <t>+27.7%</t>
         </is>
       </c>
     </row>
@@ -10049,81 +10031,81 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="199" t="inlineStr">
+      <c r="A26" s="194" t="inlineStr">
         <is>
           <t>بدجت</t>
         </is>
       </c>
-      <c r="B26" s="200" t="inlineStr">
+      <c r="B26" s="195" t="inlineStr">
         <is>
           <t>4260</t>
         </is>
       </c>
-      <c r="C26" s="201" t="n">
-        <v>38</v>
-      </c>
-      <c r="D26" s="202" t="inlineStr">
+      <c r="C26" s="196" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="D26" s="197" t="inlineStr">
         <is>
           <t>⚠ إجماع (8) — قبل انهيار Q1</t>
         </is>
       </c>
-      <c r="E26" s="203" t="n">
+      <c r="E26" s="198" t="n">
         <v>90.2</v>
       </c>
-      <c r="F26" s="204" t="inlineStr">
+      <c r="F26" s="199" t="inlineStr">
         <is>
           <t>شراء قوي — يستوجب مراجعة</t>
         </is>
       </c>
-      <c r="G26" s="205" t="inlineStr">
-        <is>
-          <t>+137.4%</t>
+      <c r="G26" s="200" t="inlineStr">
+        <is>
+          <t>+18.8%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="206" t="inlineStr"/>
-      <c r="B27" s="206" t="inlineStr"/>
-      <c r="C27" s="206" t="inlineStr"/>
-      <c r="D27" s="202" t="inlineStr">
+      <c r="A27" s="201" t="inlineStr"/>
+      <c r="B27" s="201" t="inlineStr"/>
+      <c r="C27" s="201" t="inlineStr"/>
+      <c r="D27" s="197" t="inlineStr">
         <is>
           <t>الأعلى (High) — قبل Q1</t>
         </is>
       </c>
-      <c r="E27" s="203" t="n">
+      <c r="E27" s="198" t="n">
         <v>100</v>
       </c>
-      <c r="F27" s="204" t="inlineStr">
+      <c r="F27" s="199" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G27" s="205" t="inlineStr">
-        <is>
-          <t>+163.2%</t>
+      <c r="G27" s="200" t="inlineStr">
+        <is>
+          <t>+31.8%</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="206" t="inlineStr"/>
-      <c r="B28" s="206" t="inlineStr"/>
-      <c r="C28" s="206" t="inlineStr"/>
-      <c r="D28" s="202" t="inlineStr">
+      <c r="A28" s="201" t="inlineStr"/>
+      <c r="B28" s="201" t="inlineStr"/>
+      <c r="C28" s="201" t="inlineStr"/>
+      <c r="D28" s="197" t="inlineStr">
         <is>
           <t>الأدنى (Low) — قبل Q1</t>
         </is>
       </c>
-      <c r="E28" s="203" t="n">
+      <c r="E28" s="198" t="n">
         <v>80</v>
       </c>
-      <c r="F28" s="204" t="inlineStr">
+      <c r="F28" s="199" t="inlineStr">
         <is>
           <t>شراء</t>
         </is>
       </c>
-      <c r="G28" s="205" t="inlineStr">
-        <is>
-          <t>+110.5%</t>
+      <c r="G28" s="200" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
         </is>
       </c>
     </row>
@@ -10135,81 +10117,81 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="180" t="inlineStr">
+      <c r="A30" s="177" t="inlineStr">
         <is>
           <t>اكسترا</t>
         </is>
       </c>
-      <c r="B30" s="181" t="inlineStr">
+      <c r="B30" s="178" t="inlineStr">
         <is>
           <t>4003</t>
         </is>
       </c>
-      <c r="C30" s="182" t="n">
-        <v>95</v>
-      </c>
-      <c r="D30" s="183" t="inlineStr">
+      <c r="C30" s="179" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="D30" s="180" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E30" s="188" t="n">
+      <c r="E30" s="181" t="n">
         <v>111.7</v>
       </c>
-      <c r="F30" s="185" t="inlineStr">
+      <c r="F30" s="182" t="inlineStr">
         <is>
           <t>شراء قوي (Strong Buy)</t>
         </is>
       </c>
-      <c r="G30" s="189" t="inlineStr">
-        <is>
-          <t>+17.6%</t>
+      <c r="G30" s="183" t="inlineStr">
+        <is>
+          <t>+36.4%</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="187" t="inlineStr"/>
-      <c r="B31" s="187" t="inlineStr"/>
-      <c r="C31" s="187" t="inlineStr"/>
-      <c r="D31" s="183" t="inlineStr">
+      <c r="A31" s="184" t="inlineStr"/>
+      <c r="B31" s="184" t="inlineStr"/>
+      <c r="C31" s="184" t="inlineStr"/>
+      <c r="D31" s="180" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E31" s="188" t="n">
+      <c r="E31" s="181" t="n">
         <v>140</v>
       </c>
-      <c r="F31" s="185" t="inlineStr">
+      <c r="F31" s="182" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G31" s="189" t="inlineStr">
-        <is>
-          <t>+47.4%</t>
+      <c r="G31" s="183" t="inlineStr">
+        <is>
+          <t>+70.9%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="187" t="inlineStr"/>
-      <c r="B32" s="187" t="inlineStr"/>
-      <c r="C32" s="187" t="inlineStr"/>
-      <c r="D32" s="183" t="inlineStr">
+      <c r="A32" s="184" t="inlineStr"/>
+      <c r="B32" s="184" t="inlineStr"/>
+      <c r="C32" s="184" t="inlineStr"/>
+      <c r="D32" s="180" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E32" s="184" t="n">
+      <c r="E32" s="181" t="n">
         <v>93</v>
       </c>
-      <c r="F32" s="185" t="inlineStr">
+      <c r="F32" s="182" t="inlineStr">
         <is>
           <t>شراء</t>
         </is>
       </c>
-      <c r="G32" s="186" t="inlineStr">
-        <is>
-          <t>-2.1%</t>
+      <c r="G32" s="183" t="inlineStr">
+        <is>
+          <t>+13.6%</t>
         </is>
       </c>
     </row>
@@ -10226,76 +10208,76 @@
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B34" s="207" t="inlineStr">
+      <c r="B34" s="202" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
       <c r="C34" s="120" t="n">
-        <v>48</v>
-      </c>
-      <c r="D34" s="208" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="D34" s="203" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E34" s="209" t="n">
+      <c r="E34" s="204" t="n">
         <v>38.8</v>
       </c>
-      <c r="F34" s="210" t="inlineStr">
+      <c r="F34" s="205" t="inlineStr">
         <is>
           <t>محايد (Hold)</t>
         </is>
       </c>
-      <c r="G34" s="211" t="inlineStr">
-        <is>
-          <t>-19.2%</t>
+      <c r="G34" s="127" t="inlineStr">
+        <is>
+          <t>+29.3%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="212" t="inlineStr"/>
-      <c r="B35" s="212" t="inlineStr"/>
-      <c r="C35" s="212" t="inlineStr"/>
-      <c r="D35" s="208" t="inlineStr">
+      <c r="A35" s="206" t="inlineStr"/>
+      <c r="B35" s="206" t="inlineStr"/>
+      <c r="C35" s="206" t="inlineStr"/>
+      <c r="D35" s="203" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E35" s="213" t="n">
+      <c r="E35" s="204" t="n">
         <v>50</v>
       </c>
-      <c r="F35" s="210" t="inlineStr">
+      <c r="F35" s="205" t="inlineStr">
         <is>
           <t>شراء — عند التعافي</t>
         </is>
       </c>
       <c r="G35" s="127" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+66.7%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="212" t="inlineStr"/>
-      <c r="B36" s="212" t="inlineStr"/>
-      <c r="C36" s="212" t="inlineStr"/>
-      <c r="D36" s="208" t="inlineStr">
+      <c r="A36" s="206" t="inlineStr"/>
+      <c r="B36" s="206" t="inlineStr"/>
+      <c r="C36" s="206" t="inlineStr"/>
+      <c r="D36" s="203" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E36" s="209" t="n">
+      <c r="E36" s="204" t="n">
         <v>31.1</v>
       </c>
-      <c r="F36" s="210" t="inlineStr">
+      <c r="F36" s="205" t="inlineStr">
         <is>
           <t>بيع / تخفيض</t>
         </is>
       </c>
-      <c r="G36" s="211" t="inlineStr">
-        <is>
-          <t>-35.2%</t>
+      <c r="G36" s="207" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
         </is>
       </c>
     </row>
@@ -10307,30 +10289,30 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="147" t="inlineStr">
+      <c r="A38" s="146" t="inlineStr">
         <is>
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B38" s="214" t="inlineStr">
+      <c r="B38" s="208" t="inlineStr">
         <is>
           <t>4340</t>
         </is>
       </c>
-      <c r="C38" s="148" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D38" s="215" t="inlineStr">
+      <c r="C38" s="147" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D38" s="209" t="inlineStr">
         <is>
           <t>لا تغطية موثقة من بيوت خبرة</t>
         </is>
       </c>
-      <c r="E38" s="216" t="inlineStr">
+      <c r="E38" s="210" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="217" t="inlineStr">
+      <c r="F38" s="211" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10349,7 +10331,7 @@
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="218" t="inlineStr">
+      <c r="A41" s="212" t="inlineStr">
         <is>
           <t>🟢 Upside &gt; +5%  =  فرصة رأسمالية   |   🟡 بين ±5%  =  تقييم عادل   |   🔴 Downside &gt; -5%  =  مكلف أو بلغ هدفه</t>
         </is>
@@ -10436,12 +10418,12 @@
           <t>الراجحي</t>
         </is>
       </c>
-      <c r="B3" s="219" t="inlineStr">
+      <c r="B3" s="213" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C3" s="155" t="inlineStr">
+      <c r="C3" s="154" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -10451,12 +10433,12 @@
           <t>18,000 ريال</t>
         </is>
       </c>
-      <c r="E3" s="220" t="inlineStr">
+      <c r="E3" s="214" t="inlineStr">
         <is>
           <t>نواة البنوك الإسلامية · توزيعات مستقرة · رؤية 2030</t>
         </is>
       </c>
-      <c r="F3" s="221" t="inlineStr">
+      <c r="F3" s="215" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10468,12 +10450,12 @@
           <t>STC</t>
         </is>
       </c>
-      <c r="B4" s="219" t="inlineStr">
+      <c r="B4" s="213" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C4" s="155" t="inlineStr">
+      <c r="C4" s="154" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -10483,12 +10465,12 @@
           <t>15,000 ريال</t>
         </is>
       </c>
-      <c r="E4" s="220" t="inlineStr">
+      <c r="E4" s="214" t="inlineStr">
         <is>
           <t>أعلى عائد توزيع · البنية الرقمية الوطنية</t>
         </is>
       </c>
-      <c r="F4" s="155" t="inlineStr">
+      <c r="F4" s="154" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
@@ -10500,12 +10482,12 @@
           <t>اكسترا</t>
         </is>
       </c>
-      <c r="B5" s="222" t="inlineStr">
+      <c r="B5" s="216" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C5" s="223" t="inlineStr">
+      <c r="C5" s="217" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10515,12 +10497,12 @@
           <t>12,000 ريال</t>
         </is>
       </c>
-      <c r="E5" s="224" t="inlineStr">
+      <c r="E5" s="218" t="inlineStr">
         <is>
           <t>قطاع التجزئة الدفاعي · توزيعات ممتازة · هامش أمان جيد</t>
         </is>
       </c>
-      <c r="F5" s="225" t="inlineStr">
+      <c r="F5" s="219" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10532,12 +10514,12 @@
           <t>المواساة</t>
         </is>
       </c>
-      <c r="B6" s="222" t="inlineStr">
+      <c r="B6" s="216" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C6" s="223" t="inlineStr">
+      <c r="C6" s="217" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10547,12 +10529,12 @@
           <t>10,000 ريال</t>
         </is>
       </c>
-      <c r="E6" s="224" t="inlineStr">
+      <c r="E6" s="218" t="inlineStr">
         <is>
           <t>رعاية صحية دفاعية · توزيع سنوي منتظم</t>
         </is>
       </c>
-      <c r="F6" s="223" t="inlineStr">
+      <c r="F6" s="217" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
@@ -10564,12 +10546,12 @@
           <t>الإنماء</t>
         </is>
       </c>
-      <c r="B7" s="226" t="inlineStr">
+      <c r="B7" s="220" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C7" s="227" t="inlineStr">
+      <c r="C7" s="221" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10579,12 +10561,12 @@
           <t>10,000 ريال</t>
         </is>
       </c>
-      <c r="E7" s="228" t="inlineStr">
+      <c r="E7" s="222" t="inlineStr">
         <is>
           <t>أسرع البنوك نمواً · تراجع تقييم يوفر دخولاً جيدة</t>
         </is>
       </c>
-      <c r="F7" s="229" t="inlineStr">
+      <c r="F7" s="223" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10596,12 +10578,12 @@
           <t>سال</t>
         </is>
       </c>
-      <c r="B8" s="226" t="inlineStr">
+      <c r="B8" s="220" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C8" s="230" t="inlineStr">
+      <c r="C8" s="224" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -10611,12 +10593,12 @@
           <t>7,000 ريال</t>
         </is>
       </c>
-      <c r="E8" s="228" t="inlineStr">
+      <c r="E8" s="222" t="inlineStr">
         <is>
           <t>الاستفادة من نمو قطاع الخدمات اللوجستية الجوية</t>
         </is>
       </c>
-      <c r="F8" s="231" t="inlineStr">
+      <c r="F8" s="225" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -10628,12 +10610,12 @@
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B9" s="222" t="inlineStr">
+      <c r="B9" s="216" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C9" s="232" t="inlineStr">
+      <c r="C9" s="226" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -10643,12 +10625,12 @@
           <t>8,000 ريال</t>
         </is>
       </c>
-      <c r="E9" s="224" t="inlineStr">
+      <c r="E9" s="218" t="inlineStr">
         <is>
           <t>دخل إيجاري ثابت · عائد توزيع مرتفع · تنويع القطاعات</t>
         </is>
       </c>
-      <c r="F9" s="225" t="inlineStr">
+      <c r="F9" s="219" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10660,12 +10642,12 @@
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B10" s="219" t="inlineStr">
+      <c r="B10" s="213" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C10" s="233" t="inlineStr">
+      <c r="C10" s="227" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10675,83 +10657,83 @@
           <t>5,000 ريال</t>
         </is>
       </c>
-      <c r="E10" s="220" t="inlineStr">
+      <c r="E10" s="214" t="inlineStr">
         <is>
           <t>وزن محدود · مضاربة على العودة للربحية + رؤية 2030</t>
         </is>
       </c>
-      <c r="F10" s="234" t="inlineStr">
+      <c r="F10" s="228" t="inlineStr">
         <is>
           <t>مرتفع</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="235" t="inlineStr">
+      <c r="A11" s="229" t="inlineStr">
         <is>
           <t>بدجت</t>
         </is>
       </c>
-      <c r="B11" s="236" t="inlineStr">
+      <c r="B11" s="230" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C11" s="237" t="inlineStr">
+      <c r="C11" s="231" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" s="238" t="inlineStr">
+      <c r="D11" s="232" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="239" t="inlineStr">
+      <c r="E11" s="233" t="inlineStr">
         <is>
           <t>⚠ تأجيل حتى توضيح أسباب تراجع Q1 2026</t>
         </is>
       </c>
-      <c r="F11" s="240" t="inlineStr">
+      <c r="F11" s="234" t="inlineStr">
         <is>
           <t>متوسط-مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="241" t="inlineStr">
+      <c r="A12" s="235" t="inlineStr">
         <is>
           <t>كاش</t>
         </is>
       </c>
-      <c r="B12" s="242" t="inlineStr">
+      <c r="B12" s="236" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C12" s="243" t="inlineStr">
+      <c r="C12" s="237" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D12" s="244" t="inlineStr">
+      <c r="D12" s="238" t="inlineStr">
         <is>
           <t>15,000 ريال</t>
         </is>
       </c>
-      <c r="E12" s="245" t="inlineStr">
+      <c r="E12" s="239" t="inlineStr">
         <is>
           <t>احتياطي للشراء عند الانخفاض · الحد الأدنى المقترح</t>
         </is>
       </c>
-      <c r="F12" s="246" t="inlineStr">
+      <c r="F12" s="240" t="inlineStr">
         <is>
           <t>صفر</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="241" t="inlineStr">
         <is>
           <t>استراتيجية الشراء التدريجي (Staggered Entry):
 • المرحلة 1 (الآن): الراجحي + STC + اكسترا + المواساة = 55% من المحفظة (على دفعتين)
@@ -10802,132 +10784,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>69.09999999999999</v>
+      <c r="B3" s="244" t="n">
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>2.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>20.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -10954,80 +10936,80 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>23500</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>30100</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>29800</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>34200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>14979</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>17151</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>16621</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>19722</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>12000</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>16000</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>14500</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>18500</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تمويل مشاريع عملاقة + صيرفة إسلامية + تمويل الأفراد + رقمنة الخدمات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: متطلبات كفاية رأس المال (SAMA) · تأثير المنح على المعدلات للسهم · تنافسية ضيقة</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
-        <is>
-          <t>⚠ تنبيه: ⚠ منح سهم لكل سهمين في H2 2025 → سترتفع الأسهم إلى 6,000M</t>
+      <c r="A22" s="253" t="inlineStr">
+        <is>
+          <t>⚠ تنبيه: ✅ سعر مُعدَّل بعد المنح (1 سهم / 2) → الأسهم ارتفعت من 4B إلى 6B</t>
         </is>
       </c>
     </row>
@@ -11068,132 +11050,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="248" t="inlineStr">
+      <c r="A2" s="242" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="248" t="inlineStr">
+      <c r="B2" s="242" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="249" t="inlineStr">
+      <c r="A3" s="243" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="250" t="n">
-        <v>27.5</v>
+      <c r="B3" s="244" t="n">
+        <v>23.53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="245" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="252" t="n">
+      <c r="B4" s="246" t="n">
         <v>19922</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="249" t="inlineStr">
+      <c r="A5" s="243" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="250" t="n">
+      <c r="B5" s="244" t="n">
         <v>1992</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="inlineStr">
+      <c r="A6" s="245" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="252" t="n">
+      <c r="B6" s="246" t="n">
         <v>9.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="249" t="inlineStr">
+      <c r="A7" s="243" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="250" t="n">
+      <c r="B7" s="244" t="n">
         <v>1.86</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="inlineStr">
+      <c r="A8" s="245" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="252" t="n">
+      <c r="B8" s="246" t="n">
         <v>4.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="249" t="inlineStr">
+      <c r="A9" s="243" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="250" t="n">
+      <c r="B9" s="244" t="n">
         <v>21.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="inlineStr">
+      <c r="A10" s="245" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="252" t="inlineStr">
+      <c r="B10" s="246" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="249" t="inlineStr">
+      <c r="A11" s="243" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="250" t="inlineStr">
+      <c r="B11" s="244" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="inlineStr">
+      <c r="A12" s="245" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="252" t="inlineStr">
+      <c r="B12" s="246" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="253" t="inlineStr">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="254" t="inlineStr">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -11220,78 +11202,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="255" t="inlineStr">
+      <c r="A16" s="249" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="250" t="n">
         <v>5500</v>
       </c>
-      <c r="C16" s="256" t="n">
+      <c r="C16" s="250" t="n">
         <v>7200</v>
       </c>
-      <c r="D16" s="256" t="n">
+      <c r="D16" s="250" t="n">
         <v>8700</v>
       </c>
-      <c r="E16" s="256" t="n">
+      <c r="E16" s="250" t="n">
         <v>10200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="255" t="inlineStr">
+      <c r="A17" s="249" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="250" t="n">
         <v>2714</v>
       </c>
-      <c r="C17" s="256" t="n">
+      <c r="C17" s="250" t="n">
         <v>3599</v>
       </c>
-      <c r="D17" s="256" t="n">
+      <c r="D17" s="250" t="n">
         <v>4839</v>
       </c>
-      <c r="E17" s="256" t="n">
+      <c r="E17" s="250" t="n">
         <v>5832</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="255" t="inlineStr">
+      <c r="A18" s="249" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="250" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="256" t="n">
+      <c r="C18" s="250" t="n">
         <v>4200</v>
       </c>
-      <c r="D18" s="256" t="n">
+      <c r="D18" s="250" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="256" t="n">
+      <c r="E18" s="250" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="257" t="inlineStr">
+      <c r="A20" s="251" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تمويل المشاريع الكبرى + تمويل الرهن العقاري + SME Lending + رقمنة</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="258" t="inlineStr">
+      <c r="A21" s="252" t="inlineStr">
         <is>
           <t>المخاطر: بنك أصغر نسبياً · انكشاف عقاري · سيولة تداول أقل</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="259" t="inlineStr">
+      <c r="A22" s="253" t="inlineStr">
         <is>
           <t>⚠ تنبيه: تحول إلى توزيعات ربعية منذ 2023</t>
         </is>

--- a/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
+++ b/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
@@ -579,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -851,7 +851,7 @@
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -932,61 +932,64 @@
     <xf numFmtId="164" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1077,6 +1080,9 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1127,6 +1133,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1187,7 +1196,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="33" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2091,132 +2103,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
+      <c r="B3" s="248" t="n">
         <v>43.54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>14.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>3.82</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>5.2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>26.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>تراكم بقوة</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2243,78 +2255,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>63000</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>67000</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>71800</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>75893</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>11100</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>12200</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>13300</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>24689</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>18000</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>20000</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>22000</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>24500</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: البنية الرقمية الوطنية + 5G + STC Pay + حلول سحابة للقطاع الحكومي</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: CAPEX مرتفع · ملكية حكومية قد تؤثر على قرارات التوزيع · منافسة موبايلي/زين</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ ربح 2024 (24.7B) يشمل بيع TAWAL (13.97B غير متكرر) → الربح الجاري ≈ 10.7B ريال</t>
         </is>
@@ -2357,132 +2369,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
-        <v>164.1</v>
+      <c r="B3" s="248" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>22.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>6.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>30.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>مراقبة / تراكم تدريجي</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2509,78 +2521,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>900</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>1100</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>1452</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>1630</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>320</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>450</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>511</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>661</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>400</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>550</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>680</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>820</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: مطار الملك سلمان الدولي + نمو الشحن الجوي + خدمات الخطوط السعودية</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: تركيز عملاء عالٍ · IPO تقييم مرتفع · بيانات تاريخية قصيرة · تذبذب الأسعار</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: IPO حديث (2022) - بيانات تاريخية محدودة | ✅ إيرادات 2024: 1.63B ريال (تحقق)</t>
         </is>
@@ -2623,132 +2635,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
+      <c r="B3" s="248" t="n">
         <v>59.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>20.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>3.35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>17.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>احتفاظ / تراكم عند الضعف</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -2775,78 +2787,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>2050</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>2400</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>2706</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>2879</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>520</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>680</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>658</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>646</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>650</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>820</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>800</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>780</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: خصخصة الصحة + التأمين الإلزامي + السياحة الطبية + توسع في المدينة</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: تراجع هامش الربح · شح الكوادر الطبية · تنافسية القطاع الخاص المتنامية</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: توزيع سنوي ثابت منذ الإدراج</t>
         </is>
@@ -2889,132 +2901,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
+      <c r="B3" s="248" t="n">
         <v>75.90000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>12.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>3.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>17.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>متوسط-مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>مراقبة - انتظار توضيح Q1 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3041,78 +3053,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>1200</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>1500</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>1750</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>1980</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>185</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>240</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>277</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>380</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>460</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>510</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>550</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: السياحة + الفعاليات والترفيه + تأجير أسطول NEOM + نمو المطارات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: ⚠ تراجع ربح Q1 2026 بـ58% · رأس مال مكثف للأسطول · منافسة منصات المشاركة</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ انخفاض أرباح Q1 2026 بنسبة 58% - يستوجب مراقبة</t>
         </is>
@@ -3155,132 +3167,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
+      <c r="B3" s="248" t="n">
         <v>81.90000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>14.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>5.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>30.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3307,78 +3319,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>4500</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>5200</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>5800</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>6781</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>280</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>340</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>390</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>534</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>350</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>430</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: نمو الإنفاق الاستهلاكي + التحول الرقمي + تراخيص جديدة + توسع جغرافي</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: منافسة أمازون.sa ونون · ضغط هوامش التجزئة · التحدي الرقمي</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ✅ توزيع استثنائي أغسطس 2024: 5 ريال/سهم من الاحتياطيات | ربح FY2024: 534.5M ريال</t>
         </is>
@@ -3421,128 +3433,128 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
-        <v>30</v>
+      <c r="B3" s="248" t="n">
+        <v>34.12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n"/>
+      <c r="B6" s="250" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n"/>
+      <c r="B9" s="248" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>مضاربة / وزن محدود</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3569,78 +3581,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>2100</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>2400</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>1900</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>1700</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>380</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>320</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>85</v>
       </c>
-      <c r="E17" s="254" t="n">
+      <c r="E17" s="258" t="n">
         <v>-259</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>450</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>380</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>180</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تحويل البلاستيك للمواد الإنشائية (NEOM) + طاقة انتاجية جديدة + تنويع المنتجات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: ⚠ دورية البتروكيماويات · خسارة 2024 · أسعار البروبيلين العالمية · منافسة صينية</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: ⚠ لا توزيعات 2023-2024 بسبب الخسارة | العودة للربحية Q1 2025</t>
         </is>
@@ -3683,132 +3695,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
+      <c r="B3" s="248" t="n">
         <v>9.25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>1630</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>14.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>1.03</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>7.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>احتفاظ للدخل</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -3835,78 +3847,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>140</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>155</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>170</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>190</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>85</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>95</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>105</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>90</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>100</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>115</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: نمو القطاع العقاري + الطلب السياحي + نمو الإيجارات التجارية</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: حساسية أسعار الفائدة · جودة المستأجرين · إعادة التقييم العقاري · تركيز الأصول</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: توزيع نصف سنوي إلزامي ≥90% من الدخل الصافي</t>
         </is>
@@ -4065,7 +4077,7 @@
         </is>
       </c>
       <c r="E4" s="25" t="n">
-        <v>66.59999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F4" s="26" t="n">
         <v>14</v>
@@ -4083,14 +4095,14 @@
         <v>19722</v>
       </c>
       <c r="K4" s="25" t="n">
-        <v>4.93</v>
+        <v>3.29</v>
       </c>
       <c r="L4" s="25" t="n">
         <v>2.71</v>
       </c>
       <c r="M4" s="24" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="N4" s="28" t="inlineStr">
@@ -4121,7 +4133,7 @@
         </is>
       </c>
       <c r="E5" s="31" t="n">
-        <v>23.53</v>
+        <v>23.86</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>9.4</v>
@@ -4233,7 +4245,7 @@
         </is>
       </c>
       <c r="E7" s="31" t="n">
-        <v>164.1</v>
+        <v>168</v>
       </c>
       <c r="F7" s="32" t="n">
         <v>22.4</v>
@@ -4457,7 +4469,7 @@
         </is>
       </c>
       <c r="E11" s="25" t="n">
-        <v>30</v>
+        <v>34.12</v>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
@@ -4598,7 +4610,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  الراجحي (1120) — مصرفي  ✅ سعر مُعدَّل بعد المنح (1 سهم / 2) → الأسهم ارتفعت من 4B إلى 6B</t>
+          <t xml:space="preserve">  الراجحي (1120) — مصرفي  ✅ بعد منح الأسهم (1 سهم مجاني لكل 2) → الأسهم أصبحت 6B سهم | سعر مُعدَّل</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9037,7 @@
         </is>
       </c>
       <c r="B4" s="83" t="n">
-        <v>66.59999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C4" s="84" t="n">
         <v>14</v>
@@ -9040,7 +9052,7 @@
         <v>1.46</v>
       </c>
       <c r="G4" s="85" t="n">
-        <v>7.8</v>
+        <v>12.2</v>
       </c>
       <c r="H4" s="88" t="n">
         <v>83</v>
@@ -9064,7 +9076,7 @@
       </c>
       <c r="N4" s="91" t="inlineStr">
         <is>
-          <t>+11.4%</t>
+          <t>+7.0%</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9087,7 @@
         </is>
       </c>
       <c r="B5" s="93" t="n">
-        <v>23.53</v>
+        <v>23.86</v>
       </c>
       <c r="C5" s="94" t="n">
         <v>9.4</v>
@@ -9090,7 +9102,7 @@
         <v>0.32</v>
       </c>
       <c r="G5" s="95" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H5" s="98" t="n">
         <v>35</v>
@@ -9114,7 +9126,7 @@
       </c>
       <c r="N5" s="101" t="inlineStr">
         <is>
-          <t>+22.4%</t>
+          <t>+20.7%</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9185,7 @@
         </is>
       </c>
       <c r="B7" s="111" t="n">
-        <v>164.1</v>
+        <v>168</v>
       </c>
       <c r="C7" s="112" t="n">
         <v>22.4</v>
@@ -9188,7 +9200,7 @@
         <v>0.82</v>
       </c>
       <c r="G7" s="113" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H7" s="116" t="n">
         <v>220</v>
@@ -9210,7 +9222,7 @@
       </c>
       <c r="N7" s="118" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+7.9%</t>
         </is>
       </c>
     </row>
@@ -9352,122 +9364,122 @@
       <c r="M10" s="116" t="n">
         <v>111.7</v>
       </c>
-      <c r="N10" s="118" t="inlineStr">
+      <c r="N10" s="137" t="inlineStr">
         <is>
           <t>+24.8%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="137" t="inlineStr">
+      <c r="A11" s="138" t="inlineStr">
         <is>
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B11" s="138" t="n">
-        <v>30</v>
-      </c>
-      <c r="C11" s="139" t="inlineStr">
+      <c r="B11" s="139" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="C11" s="140" t="inlineStr">
         <is>
           <t>خسارة</t>
         </is>
       </c>
-      <c r="D11" s="140" t="n">
+      <c r="D11" s="141" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="141" t="n">
+      <c r="E11" s="142" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="142" t="inlineStr">
+      <c r="F11" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="140" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H11" s="143" t="n">
+      <c r="G11" s="141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="144" t="n">
         <v>60</v>
       </c>
-      <c r="I11" s="142" t="inlineStr">
+      <c r="I11" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="143" t="n">
+      <c r="J11" s="144" t="n">
         <v>55</v>
       </c>
-      <c r="K11" s="142" t="inlineStr">
+      <c r="K11" s="143" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="144" t="n">
+      <c r="L11" s="145" t="n">
         <v>3.6</v>
       </c>
-      <c r="M11" s="143" t="n">
+      <c r="M11" s="144" t="n">
         <v>38.8</v>
       </c>
-      <c r="N11" s="145" t="inlineStr">
-        <is>
-          <t>+31.7%</t>
+      <c r="N11" s="146" t="inlineStr">
+        <is>
+          <t>+15.8%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="146" t="inlineStr">
+      <c r="A12" s="147" t="inlineStr">
         <is>
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B12" s="147" t="n">
+      <c r="B12" s="148" t="n">
         <v>9.25</v>
       </c>
-      <c r="C12" s="148" t="n">
+      <c r="C12" s="149" t="n">
         <v>14.1</v>
       </c>
-      <c r="D12" s="149" t="n">
+      <c r="D12" s="150" t="n">
         <v>1.03</v>
       </c>
-      <c r="E12" s="150" t="n">
+      <c r="E12" s="151" t="n">
         <v>7.5</v>
       </c>
-      <c r="F12" s="151" t="n">
+      <c r="F12" s="152" t="n">
         <v>1.22</v>
       </c>
-      <c r="G12" s="149" t="n">
+      <c r="G12" s="150" t="n">
         <v>7.9</v>
       </c>
-      <c r="H12" s="152" t="n">
+      <c r="H12" s="153" t="n">
         <v>10.8</v>
       </c>
-      <c r="I12" s="152" t="n">
+      <c r="I12" s="153" t="n">
         <v>11.5</v>
       </c>
-      <c r="J12" s="152" t="n">
+      <c r="J12" s="153" t="n">
         <v>10.5</v>
       </c>
-      <c r="K12" s="152" t="n">
+      <c r="K12" s="153" t="n">
         <v>14.8</v>
       </c>
-      <c r="L12" s="153" t="inlineStr">
+      <c r="L12" s="154" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" s="153" t="inlineStr">
+      <c r="M12" s="154" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N12" s="154" t="inlineStr">
+      <c r="N12" s="155" t="inlineStr">
         <is>
           <t>+28.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="155" t="inlineStr">
+      <c r="A14" s="156" t="inlineStr">
         <is>
           <t>منهجية: P/E = متوسط P/E قطاعي × EPS 2024  |  P/B = متوسط P/B قطاعي × القيمة الدفترية  |  DDM = DPS₁/(WACC−g)  |  DCF = Σ FCF/(1+WACC)^t + Terminal (5 سنوات، g_terminal=3%)  |  EV/EBITDA = EBITDA × Benchmark القطاعي ÷ الأسهم  |  PEG = P/E ÷ CAGR%  |  هامش الأمان = (متوسط 5 طرق − السعر) ÷ السعر  |  ⚠ DCF وEV/EBITDA تقديرات مبنية على OCF كـProxy — راجع ورقة منهجية التقييم للتفاصيل</t>
         </is>
@@ -9509,694 +9521,694 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="156" t="inlineStr">
+      <c r="A2" s="157" t="inlineStr">
         <is>
           <t>⚠ ملاحظة: أسعار بيوت الخبرة المسماة محدودة الإتاحة للعموم — البيانات المُتحقق منها تعتمد على إجماع Investing.com/Bloomberg. | ⚠ أهداف بدجت مُحتسبة قبل نتائج Q1 2026 المخيبة للآمال.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="157" t="inlineStr">
+      <c r="A3" s="158" t="inlineStr">
         <is>
           <t>الشركة</t>
         </is>
       </c>
-      <c r="B3" s="157" t="inlineStr">
+      <c r="B3" s="158" t="inlineStr">
         <is>
           <t>الرمز</t>
         </is>
       </c>
-      <c r="C3" s="157" t="inlineStr">
+      <c r="C3" s="158" t="inlineStr">
         <is>
           <t>السعر الحالي
 (ريال)</t>
         </is>
       </c>
-      <c r="D3" s="157" t="inlineStr">
+      <c r="D3" s="158" t="inlineStr">
         <is>
           <t>بيت الخبرة / المصدر</t>
         </is>
       </c>
-      <c r="E3" s="157" t="inlineStr">
+      <c r="E3" s="158" t="inlineStr">
         <is>
           <t>السعر المستهدف
 (ريال)</t>
         </is>
       </c>
-      <c r="F3" s="157" t="inlineStr">
+      <c r="F3" s="158" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="G3" s="157" t="inlineStr">
+      <c r="G3" s="158" t="inlineStr">
         <is>
           <t>Upside%</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="158" t="inlineStr">
+      <c r="A4" s="159" t="inlineStr">
         <is>
           <t>الراجحي</t>
         </is>
       </c>
-      <c r="B4" s="159" t="inlineStr">
+      <c r="B4" s="160" t="inlineStr">
         <is>
           <t>1120</t>
         </is>
       </c>
-      <c r="C4" s="160" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="D4" s="161" t="inlineStr">
+      <c r="C4" s="161" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="D4" s="162" t="inlineStr">
         <is>
           <t>الجزيرة كابيتال</t>
         </is>
       </c>
-      <c r="E4" s="162" t="n">
+      <c r="E4" s="163" t="n">
         <v>102</v>
       </c>
-      <c r="F4" s="163" t="inlineStr">
+      <c r="F4" s="164" t="inlineStr">
         <is>
           <t>زيادة المراكز (OW)</t>
         </is>
       </c>
-      <c r="G4" s="164" t="inlineStr">
-        <is>
-          <t>+53.2%</t>
+      <c r="G4" s="165" t="inlineStr">
+        <is>
+          <t>+47.1%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="165" t="inlineStr"/>
-      <c r="B5" s="165" t="inlineStr"/>
-      <c r="C5" s="165" t="inlineStr"/>
-      <c r="D5" s="161" t="inlineStr">
+      <c r="A5" s="166" t="inlineStr"/>
+      <c r="B5" s="166" t="inlineStr"/>
+      <c r="C5" s="166" t="inlineStr"/>
+      <c r="D5" s="162" t="inlineStr">
         <is>
           <t>مورغان ستانلي</t>
         </is>
       </c>
-      <c r="E5" s="162" t="n">
+      <c r="E5" s="163" t="n">
         <v>94.5</v>
       </c>
-      <c r="F5" s="163" t="inlineStr">
+      <c r="F5" s="164" t="inlineStr">
         <is>
           <t>محايد (Neutral)</t>
         </is>
       </c>
-      <c r="G5" s="164" t="inlineStr">
-        <is>
-          <t>+41.9%</t>
+      <c r="G5" s="165" t="inlineStr">
+        <is>
+          <t>+36.3%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="165" t="inlineStr"/>
-      <c r="B6" s="165" t="inlineStr"/>
-      <c r="C6" s="165" t="inlineStr"/>
-      <c r="D6" s="161" t="inlineStr">
+      <c r="A6" s="166" t="inlineStr"/>
+      <c r="B6" s="166" t="inlineStr"/>
+      <c r="C6" s="166" t="inlineStr"/>
+      <c r="D6" s="162" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E6" s="162" t="n">
+      <c r="E6" s="163" t="n">
         <v>113.5</v>
       </c>
-      <c r="F6" s="163" t="inlineStr">
+      <c r="F6" s="164" t="inlineStr">
         <is>
           <t>شراء (Buy)</t>
         </is>
       </c>
-      <c r="G6" s="164" t="inlineStr">
-        <is>
-          <t>+70.4%</t>
+      <c r="G6" s="165" t="inlineStr">
+        <is>
+          <t>+63.7%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="165" t="inlineStr"/>
-      <c r="B7" s="165" t="inlineStr"/>
-      <c r="C7" s="165" t="inlineStr"/>
-      <c r="D7" s="161" t="inlineStr">
+      <c r="A7" s="166" t="inlineStr"/>
+      <c r="B7" s="166" t="inlineStr"/>
+      <c r="C7" s="166" t="inlineStr"/>
+      <c r="D7" s="162" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E7" s="162" t="n">
+      <c r="E7" s="163" t="n">
         <v>126</v>
       </c>
-      <c r="F7" s="163" t="inlineStr">
+      <c r="F7" s="164" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G7" s="164" t="inlineStr">
-        <is>
-          <t>+89.2%</t>
+      <c r="G7" s="165" t="inlineStr">
+        <is>
+          <t>+81.7%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="165" t="inlineStr"/>
-      <c r="B8" s="165" t="inlineStr"/>
-      <c r="C8" s="165" t="inlineStr"/>
-      <c r="D8" s="161" t="inlineStr">
+      <c r="A8" s="166" t="inlineStr"/>
+      <c r="B8" s="166" t="inlineStr"/>
+      <c r="C8" s="166" t="inlineStr"/>
+      <c r="D8" s="162" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E8" s="162" t="n">
+      <c r="E8" s="163" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="F8" s="163" t="inlineStr">
+      <c r="F8" s="164" t="inlineStr">
         <is>
           <t>شراء</t>
         </is>
       </c>
-      <c r="G8" s="164" t="inlineStr">
-        <is>
-          <t>+49.2%</t>
+      <c r="G8" s="165" t="inlineStr">
+        <is>
+          <t>+43.3%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="166" t="inlineStr">
+      <c r="A9" s="167" t="inlineStr">
         <is>
           <t>الإجماع: متوسط 113.5 | نطاق 99.4–126.0 | 8 محللين | شراء | مايو 2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="158" t="inlineStr">
+      <c r="A10" s="159" t="inlineStr">
         <is>
           <t>الإنماء</t>
         </is>
       </c>
-      <c r="B10" s="159" t="inlineStr">
+      <c r="B10" s="160" t="inlineStr">
         <is>
           <t>1150</t>
         </is>
       </c>
-      <c r="C10" s="160" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="D10" s="161" t="inlineStr">
+      <c r="C10" s="161" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="D10" s="162" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E10" s="162" t="n">
+      <c r="E10" s="163" t="n">
         <v>27.6</v>
       </c>
-      <c r="F10" s="163" t="inlineStr">
+      <c r="F10" s="164" t="inlineStr">
         <is>
           <t>شراء (Buy)</t>
         </is>
       </c>
-      <c r="G10" s="164" t="inlineStr">
-        <is>
-          <t>+17.3%</t>
+      <c r="G10" s="165" t="inlineStr">
+        <is>
+          <t>+15.7%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="165" t="inlineStr"/>
-      <c r="B11" s="165" t="inlineStr"/>
-      <c r="C11" s="165" t="inlineStr"/>
-      <c r="D11" s="161" t="inlineStr">
+      <c r="A11" s="166" t="inlineStr"/>
+      <c r="B11" s="166" t="inlineStr"/>
+      <c r="C11" s="166" t="inlineStr"/>
+      <c r="D11" s="162" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E11" s="162" t="n">
+      <c r="E11" s="163" t="n">
         <v>41</v>
       </c>
-      <c r="F11" s="163" t="inlineStr">
+      <c r="F11" s="164" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G11" s="164" t="inlineStr">
-        <is>
-          <t>+74.2%</t>
+      <c r="G11" s="165" t="inlineStr">
+        <is>
+          <t>+71.8%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="165" t="inlineStr"/>
-      <c r="B12" s="165" t="inlineStr"/>
-      <c r="C12" s="165" t="inlineStr"/>
-      <c r="D12" s="161" t="inlineStr">
+      <c r="A12" s="166" t="inlineStr"/>
+      <c r="B12" s="166" t="inlineStr"/>
+      <c r="C12" s="166" t="inlineStr"/>
+      <c r="D12" s="162" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E12" s="162" t="n">
+      <c r="E12" s="163" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="163" t="inlineStr">
+      <c r="F12" s="164" t="inlineStr">
         <is>
           <t>محايد</t>
         </is>
       </c>
-      <c r="G12" s="164" t="inlineStr">
+      <c r="G12" s="168" t="inlineStr">
+        <is>
+          <t>+4.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="167" t="inlineStr">
+        <is>
+          <t>الإجماع: متوسط 27.6 | نطاق 25.0–41.0 | 8 محللين | شراء | مايو 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="169" t="inlineStr">
+        <is>
+          <t>STC</t>
+        </is>
+      </c>
+      <c r="B14" s="170" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="D14" s="172" t="inlineStr">
+        <is>
+          <t>إجماع (8 محللين)</t>
+        </is>
+      </c>
+      <c r="E14" s="173" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="F14" s="174" t="inlineStr">
+        <is>
+          <t>شراء (Buy)</t>
+        </is>
+      </c>
+      <c r="G14" s="175" t="inlineStr">
+        <is>
+          <t>+9.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="176" t="inlineStr"/>
+      <c r="B15" s="176" t="inlineStr"/>
+      <c r="C15" s="176" t="inlineStr"/>
+      <c r="D15" s="172" t="inlineStr">
+        <is>
+          <t>الأعلى (High)</t>
+        </is>
+      </c>
+      <c r="E15" s="173" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" s="174" t="inlineStr">
+        <is>
+          <t>شراء قوي</t>
+        </is>
+      </c>
+      <c r="G15" s="175" t="inlineStr">
+        <is>
+          <t>+26.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="176" t="inlineStr"/>
+      <c r="B16" s="176" t="inlineStr"/>
+      <c r="C16" s="176" t="inlineStr"/>
+      <c r="D16" s="172" t="inlineStr">
+        <is>
+          <t>الأدنى (Low)</t>
+        </is>
+      </c>
+      <c r="E16" s="177" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F16" s="174" t="inlineStr">
+        <is>
+          <t>محايد</t>
+        </is>
+      </c>
+      <c r="G16" s="178" t="inlineStr">
+        <is>
+          <t>-5.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="167" t="inlineStr">
+        <is>
+          <t>الإجماع: متوسط 47.7 | نطاق 41.1–55.0 | 8 محللين | شراء | مايو 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="179" t="inlineStr">
+        <is>
+          <t>سال</t>
+        </is>
+      </c>
+      <c r="B18" s="180" t="inlineStr">
+        <is>
+          <t>4263</t>
+        </is>
+      </c>
+      <c r="C18" s="181" t="n">
+        <v>168</v>
+      </c>
+      <c r="D18" s="182" t="inlineStr">
+        <is>
+          <t>إجماع المحللين</t>
+        </is>
+      </c>
+      <c r="E18" s="183" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="F18" s="184" t="inlineStr">
+        <is>
+          <t>محايد (Neutral)</t>
+        </is>
+      </c>
+      <c r="G18" s="185" t="inlineStr">
         <is>
           <t>+6.2%</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="166" t="inlineStr">
-        <is>
-          <t>الإجماع: متوسط 27.6 | نطاق 25.0–41.0 | 8 محللين | شراء | مايو 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="167" t="inlineStr">
-        <is>
-          <t>STC</t>
-        </is>
-      </c>
-      <c r="B14" s="168" t="inlineStr">
-        <is>
-          <t>7010</t>
-        </is>
-      </c>
-      <c r="C14" s="169" t="n">
-        <v>43.54</v>
-      </c>
-      <c r="D14" s="170" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="186" t="inlineStr"/>
+      <c r="B19" s="186" t="inlineStr"/>
+      <c r="C19" s="186" t="inlineStr"/>
+      <c r="D19" s="182" t="inlineStr">
+        <is>
+          <t>الأعلى (High)</t>
+        </is>
+      </c>
+      <c r="E19" s="183" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="F19" s="184" t="inlineStr">
+        <is>
+          <t>شراء</t>
+        </is>
+      </c>
+      <c r="G19" s="185" t="inlineStr">
+        <is>
+          <t>+16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="186" t="inlineStr"/>
+      <c r="B20" s="186" t="inlineStr"/>
+      <c r="C20" s="186" t="inlineStr"/>
+      <c r="D20" s="182" t="inlineStr">
+        <is>
+          <t>الأدنى (Low)</t>
+        </is>
+      </c>
+      <c r="E20" s="187" t="n">
+        <v>165</v>
+      </c>
+      <c r="F20" s="184" t="inlineStr">
+        <is>
+          <t>محايد</t>
+        </is>
+      </c>
+      <c r="G20" s="188" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="167" t="inlineStr">
+        <is>
+          <t>الإجماع: متوسط 178.4 | نطاق 165.0–196.1 | ? محللين | محايد | مايو 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="189" t="inlineStr">
+        <is>
+          <t>المواساة</t>
+        </is>
+      </c>
+      <c r="B22" s="190" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="C22" s="191" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="D22" s="192" t="inlineStr">
+        <is>
+          <t>إجماع (5+ محللين)</t>
+        </is>
+      </c>
+      <c r="E22" s="193" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="F22" s="194" t="inlineStr">
+        <is>
+          <t>شراء (Buy)</t>
+        </is>
+      </c>
+      <c r="G22" s="195" t="inlineStr">
+        <is>
+          <t>+55.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="196" t="inlineStr"/>
+      <c r="B23" s="196" t="inlineStr"/>
+      <c r="C23" s="196" t="inlineStr"/>
+      <c r="D23" s="192" t="inlineStr">
+        <is>
+          <t>الأعلى (High)</t>
+        </is>
+      </c>
+      <c r="E23" s="193" t="n">
+        <v>125</v>
+      </c>
+      <c r="F23" s="194" t="inlineStr">
+        <is>
+          <t>شراء قوي</t>
+        </is>
+      </c>
+      <c r="G23" s="195" t="inlineStr">
+        <is>
+          <t>+111.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="196" t="inlineStr"/>
+      <c r="B24" s="196" t="inlineStr"/>
+      <c r="C24" s="196" t="inlineStr"/>
+      <c r="D24" s="192" t="inlineStr">
+        <is>
+          <t>الأدنى (Low)</t>
+        </is>
+      </c>
+      <c r="E24" s="193" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F24" s="194" t="inlineStr">
+        <is>
+          <t>محايد</t>
+        </is>
+      </c>
+      <c r="G24" s="195" t="inlineStr">
+        <is>
+          <t>+27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="167" t="inlineStr">
+        <is>
+          <t>الإجماع: متوسط 91.6 | نطاق 75.5–125.0 | 5 محللين | شراء | مايو 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="197" t="inlineStr">
+        <is>
+          <t>بدجت</t>
+        </is>
+      </c>
+      <c r="B26" s="198" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="C26" s="199" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="D26" s="200" t="inlineStr">
+        <is>
+          <t>⚠ إجماع (8) — قبل انهيار Q1</t>
+        </is>
+      </c>
+      <c r="E26" s="201" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="F26" s="202" t="inlineStr">
+        <is>
+          <t>شراء قوي — يستوجب مراجعة</t>
+        </is>
+      </c>
+      <c r="G26" s="203" t="inlineStr">
+        <is>
+          <t>+18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="204" t="inlineStr"/>
+      <c r="B27" s="204" t="inlineStr"/>
+      <c r="C27" s="204" t="inlineStr"/>
+      <c r="D27" s="200" t="inlineStr">
+        <is>
+          <t>الأعلى (High) — قبل Q1</t>
+        </is>
+      </c>
+      <c r="E27" s="201" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" s="202" t="inlineStr">
+        <is>
+          <t>شراء قوي</t>
+        </is>
+      </c>
+      <c r="G27" s="203" t="inlineStr">
+        <is>
+          <t>+31.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="204" t="inlineStr"/>
+      <c r="B28" s="204" t="inlineStr"/>
+      <c r="C28" s="204" t="inlineStr"/>
+      <c r="D28" s="200" t="inlineStr">
+        <is>
+          <t>الأدنى (Low) — قبل Q1</t>
+        </is>
+      </c>
+      <c r="E28" s="201" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" s="202" t="inlineStr">
+        <is>
+          <t>شراء</t>
+        </is>
+      </c>
+      <c r="G28" s="203" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="167" t="inlineStr">
+        <is>
+          <t>الإجماع: متوسط 90.2 | نطاق 80.0–100.0 | 8 محللين | ⚠ شراء قوي (قبل Q1 2026) | ⚠ سابق لنتائج Q1 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="179" t="inlineStr">
+        <is>
+          <t>اكسترا</t>
+        </is>
+      </c>
+      <c r="B30" s="180" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="C30" s="181" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="D30" s="182" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E14" s="171" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="F14" s="172" t="inlineStr">
-        <is>
-          <t>شراء (Buy)</t>
-        </is>
-      </c>
-      <c r="G14" s="173" t="inlineStr">
-        <is>
-          <t>+9.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="174" t="inlineStr"/>
-      <c r="B15" s="174" t="inlineStr"/>
-      <c r="C15" s="174" t="inlineStr"/>
-      <c r="D15" s="170" t="inlineStr">
+      <c r="E30" s="183" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="F30" s="184" t="inlineStr">
+        <is>
+          <t>شراء قوي (Strong Buy)</t>
+        </is>
+      </c>
+      <c r="G30" s="185" t="inlineStr">
+        <is>
+          <t>+36.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="186" t="inlineStr"/>
+      <c r="B31" s="186" t="inlineStr"/>
+      <c r="C31" s="186" t="inlineStr"/>
+      <c r="D31" s="182" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E15" s="171" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" s="172" t="inlineStr">
+      <c r="E31" s="183" t="n">
+        <v>140</v>
+      </c>
+      <c r="F31" s="184" t="inlineStr">
         <is>
           <t>شراء قوي</t>
         </is>
       </c>
-      <c r="G15" s="173" t="inlineStr">
-        <is>
-          <t>+26.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="174" t="inlineStr"/>
-      <c r="B16" s="174" t="inlineStr"/>
-      <c r="C16" s="174" t="inlineStr"/>
-      <c r="D16" s="170" t="inlineStr">
+      <c r="G31" s="185" t="inlineStr">
+        <is>
+          <t>+70.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="186" t="inlineStr"/>
+      <c r="B32" s="186" t="inlineStr"/>
+      <c r="C32" s="186" t="inlineStr"/>
+      <c r="D32" s="182" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E16" s="175" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="F16" s="172" t="inlineStr">
-        <is>
-          <t>محايد</t>
-        </is>
-      </c>
-      <c r="G16" s="176" t="inlineStr">
-        <is>
-          <t>-5.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="166" t="inlineStr">
-        <is>
-          <t>الإجماع: متوسط 47.7 | نطاق 41.1–55.0 | 8 محللين | شراء | مايو 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="177" t="inlineStr">
-        <is>
-          <t>سال</t>
-        </is>
-      </c>
-      <c r="B18" s="178" t="inlineStr">
-        <is>
-          <t>4263</t>
-        </is>
-      </c>
-      <c r="C18" s="179" t="n">
-        <v>164.1</v>
-      </c>
-      <c r="D18" s="180" t="inlineStr">
-        <is>
-          <t>إجماع المحللين</t>
-        </is>
-      </c>
-      <c r="E18" s="181" t="n">
-        <v>178.4</v>
-      </c>
-      <c r="F18" s="182" t="inlineStr">
-        <is>
-          <t>محايد (Neutral)</t>
-        </is>
-      </c>
-      <c r="G18" s="183" t="inlineStr">
-        <is>
-          <t>+8.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="184" t="inlineStr"/>
-      <c r="B19" s="184" t="inlineStr"/>
-      <c r="C19" s="184" t="inlineStr"/>
-      <c r="D19" s="180" t="inlineStr">
-        <is>
-          <t>الأعلى (High)</t>
-        </is>
-      </c>
-      <c r="E19" s="181" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="F19" s="182" t="inlineStr">
+      <c r="E32" s="183" t="n">
+        <v>93</v>
+      </c>
+      <c r="F32" s="184" t="inlineStr">
         <is>
           <t>شراء</t>
         </is>
       </c>
-      <c r="G19" s="183" t="inlineStr">
-        <is>
-          <t>+19.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="184" t="inlineStr"/>
-      <c r="B20" s="184" t="inlineStr"/>
-      <c r="C20" s="184" t="inlineStr"/>
-      <c r="D20" s="180" t="inlineStr">
-        <is>
-          <t>الأدنى (Low)</t>
-        </is>
-      </c>
-      <c r="E20" s="181" t="n">
-        <v>165</v>
-      </c>
-      <c r="F20" s="182" t="inlineStr">
-        <is>
-          <t>محايد</t>
-        </is>
-      </c>
-      <c r="G20" s="185" t="inlineStr">
-        <is>
-          <t>+0.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="166" t="inlineStr">
-        <is>
-          <t>الإجماع: متوسط 178.4 | نطاق 165.0–196.1 | ? محللين | محايد | مايو 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="186" t="inlineStr">
-        <is>
-          <t>المواساة</t>
-        </is>
-      </c>
-      <c r="B22" s="187" t="inlineStr">
-        <is>
-          <t>4002</t>
-        </is>
-      </c>
-      <c r="C22" s="188" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="D22" s="189" t="inlineStr">
-        <is>
-          <t>إجماع (5+ محللين)</t>
-        </is>
-      </c>
-      <c r="E22" s="190" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="F22" s="191" t="inlineStr">
-        <is>
-          <t>شراء (Buy)</t>
-        </is>
-      </c>
-      <c r="G22" s="192" t="inlineStr">
-        <is>
-          <t>+55.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="193" t="inlineStr"/>
-      <c r="B23" s="193" t="inlineStr"/>
-      <c r="C23" s="193" t="inlineStr"/>
-      <c r="D23" s="189" t="inlineStr">
-        <is>
-          <t>الأعلى (High)</t>
-        </is>
-      </c>
-      <c r="E23" s="190" t="n">
-        <v>125</v>
-      </c>
-      <c r="F23" s="191" t="inlineStr">
-        <is>
-          <t>شراء قوي</t>
-        </is>
-      </c>
-      <c r="G23" s="192" t="inlineStr">
-        <is>
-          <t>+111.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="193" t="inlineStr"/>
-      <c r="B24" s="193" t="inlineStr"/>
-      <c r="C24" s="193" t="inlineStr"/>
-      <c r="D24" s="189" t="inlineStr">
-        <is>
-          <t>الأدنى (Low)</t>
-        </is>
-      </c>
-      <c r="E24" s="190" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="F24" s="191" t="inlineStr">
-        <is>
-          <t>محايد</t>
-        </is>
-      </c>
-      <c r="G24" s="192" t="inlineStr">
-        <is>
-          <t>+27.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="166" t="inlineStr">
-        <is>
-          <t>الإجماع: متوسط 91.6 | نطاق 75.5–125.0 | 5 محللين | شراء | مايو 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="194" t="inlineStr">
-        <is>
-          <t>بدجت</t>
-        </is>
-      </c>
-      <c r="B26" s="195" t="inlineStr">
-        <is>
-          <t>4260</t>
-        </is>
-      </c>
-      <c r="C26" s="196" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="D26" s="197" t="inlineStr">
-        <is>
-          <t>⚠ إجماع (8) — قبل انهيار Q1</t>
-        </is>
-      </c>
-      <c r="E26" s="198" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F26" s="199" t="inlineStr">
-        <is>
-          <t>شراء قوي — يستوجب مراجعة</t>
-        </is>
-      </c>
-      <c r="G26" s="200" t="inlineStr">
-        <is>
-          <t>+18.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="201" t="inlineStr"/>
-      <c r="B27" s="201" t="inlineStr"/>
-      <c r="C27" s="201" t="inlineStr"/>
-      <c r="D27" s="197" t="inlineStr">
-        <is>
-          <t>الأعلى (High) — قبل Q1</t>
-        </is>
-      </c>
-      <c r="E27" s="198" t="n">
-        <v>100</v>
-      </c>
-      <c r="F27" s="199" t="inlineStr">
-        <is>
-          <t>شراء قوي</t>
-        </is>
-      </c>
-      <c r="G27" s="200" t="inlineStr">
-        <is>
-          <t>+31.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="201" t="inlineStr"/>
-      <c r="B28" s="201" t="inlineStr"/>
-      <c r="C28" s="201" t="inlineStr"/>
-      <c r="D28" s="197" t="inlineStr">
-        <is>
-          <t>الأدنى (Low) — قبل Q1</t>
-        </is>
-      </c>
-      <c r="E28" s="198" t="n">
-        <v>80</v>
-      </c>
-      <c r="F28" s="199" t="inlineStr">
-        <is>
-          <t>شراء</t>
-        </is>
-      </c>
-      <c r="G28" s="200" t="inlineStr">
-        <is>
-          <t>+5.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="166" t="inlineStr">
-        <is>
-          <t>الإجماع: متوسط 90.2 | نطاق 80.0–100.0 | 8 محللين | ⚠ شراء قوي (قبل Q1 2026) | ⚠ سابق لنتائج Q1 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="177" t="inlineStr">
-        <is>
-          <t>اكسترا</t>
-        </is>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="C30" s="179" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="D30" s="180" t="inlineStr">
-        <is>
-          <t>إجماع (8 محللين)</t>
-        </is>
-      </c>
-      <c r="E30" s="181" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="F30" s="182" t="inlineStr">
-        <is>
-          <t>شراء قوي (Strong Buy)</t>
-        </is>
-      </c>
-      <c r="G30" s="183" t="inlineStr">
-        <is>
-          <t>+36.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="184" t="inlineStr"/>
-      <c r="B31" s="184" t="inlineStr"/>
-      <c r="C31" s="184" t="inlineStr"/>
-      <c r="D31" s="180" t="inlineStr">
-        <is>
-          <t>الأعلى (High)</t>
-        </is>
-      </c>
-      <c r="E31" s="181" t="n">
-        <v>140</v>
-      </c>
-      <c r="F31" s="182" t="inlineStr">
-        <is>
-          <t>شراء قوي</t>
-        </is>
-      </c>
-      <c r="G31" s="183" t="inlineStr">
-        <is>
-          <t>+70.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="184" t="inlineStr"/>
-      <c r="B32" s="184" t="inlineStr"/>
-      <c r="C32" s="184" t="inlineStr"/>
-      <c r="D32" s="180" t="inlineStr">
-        <is>
-          <t>الأدنى (Low)</t>
-        </is>
-      </c>
-      <c r="E32" s="181" t="n">
-        <v>93</v>
-      </c>
-      <c r="F32" s="182" t="inlineStr">
-        <is>
-          <t>شراء</t>
-        </is>
-      </c>
-      <c r="G32" s="183" t="inlineStr">
+      <c r="G32" s="185" t="inlineStr">
         <is>
           <t>+13.6%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="166" t="inlineStr">
+      <c r="A33" s="167" t="inlineStr">
         <is>
           <t>الإجماع: متوسط 111.7 | نطاق 93.0–140.0 | 8 محللين | شراء قوي | مايو 2026</t>
         </is>
@@ -10208,111 +10220,111 @@
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B34" s="202" t="inlineStr">
+      <c r="B34" s="205" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
       <c r="C34" s="120" t="n">
-        <v>30</v>
-      </c>
-      <c r="D34" s="203" t="inlineStr">
+        <v>34.12</v>
+      </c>
+      <c r="D34" s="206" t="inlineStr">
         <is>
           <t>إجماع (8 محللين)</t>
         </is>
       </c>
-      <c r="E34" s="204" t="n">
+      <c r="E34" s="207" t="n">
         <v>38.8</v>
       </c>
-      <c r="F34" s="205" t="inlineStr">
+      <c r="F34" s="208" t="inlineStr">
         <is>
           <t>محايد (Hold)</t>
         </is>
       </c>
       <c r="G34" s="127" t="inlineStr">
         <is>
-          <t>+29.3%</t>
+          <t>+13.7%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="206" t="inlineStr"/>
-      <c r="B35" s="206" t="inlineStr"/>
-      <c r="C35" s="206" t="inlineStr"/>
-      <c r="D35" s="203" t="inlineStr">
+      <c r="A35" s="209" t="inlineStr"/>
+      <c r="B35" s="209" t="inlineStr"/>
+      <c r="C35" s="209" t="inlineStr"/>
+      <c r="D35" s="206" t="inlineStr">
         <is>
           <t>الأعلى (High)</t>
         </is>
       </c>
-      <c r="E35" s="204" t="n">
+      <c r="E35" s="207" t="n">
         <v>50</v>
       </c>
-      <c r="F35" s="205" t="inlineStr">
+      <c r="F35" s="208" t="inlineStr">
         <is>
           <t>شراء — عند التعافي</t>
         </is>
       </c>
       <c r="G35" s="127" t="inlineStr">
         <is>
-          <t>+66.7%</t>
+          <t>+46.5%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="206" t="inlineStr"/>
-      <c r="B36" s="206" t="inlineStr"/>
-      <c r="C36" s="206" t="inlineStr"/>
-      <c r="D36" s="203" t="inlineStr">
+      <c r="A36" s="209" t="inlineStr"/>
+      <c r="B36" s="209" t="inlineStr"/>
+      <c r="C36" s="209" t="inlineStr"/>
+      <c r="D36" s="206" t="inlineStr">
         <is>
           <t>الأدنى (Low)</t>
         </is>
       </c>
-      <c r="E36" s="204" t="n">
+      <c r="E36" s="210" t="n">
         <v>31.1</v>
       </c>
-      <c r="F36" s="205" t="inlineStr">
+      <c r="F36" s="208" t="inlineStr">
         <is>
           <t>بيع / تخفيض</t>
         </is>
       </c>
-      <c r="G36" s="207" t="inlineStr">
-        <is>
-          <t>+3.7%</t>
+      <c r="G36" s="211" t="inlineStr">
+        <is>
+          <t>-8.9%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="166" t="inlineStr">
+      <c r="A37" s="167" t="inlineStr">
         <is>
           <t>الإجماع: متوسط 38.8 | نطاق 31.1–50.0 | 8 محللين | محايد | مايو 2026</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="146" t="inlineStr">
+      <c r="A38" s="147" t="inlineStr">
         <is>
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B38" s="208" t="inlineStr">
+      <c r="B38" s="212" t="inlineStr">
         <is>
           <t>4340</t>
         </is>
       </c>
-      <c r="C38" s="147" t="n">
+      <c r="C38" s="148" t="n">
         <v>9.25</v>
       </c>
-      <c r="D38" s="209" t="inlineStr">
+      <c r="D38" s="213" t="inlineStr">
         <is>
           <t>لا تغطية موثقة من بيوت خبرة</t>
         </is>
       </c>
-      <c r="E38" s="210" t="inlineStr">
+      <c r="E38" s="214" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="211" t="inlineStr">
+      <c r="F38" s="215" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10324,14 +10336,14 @@
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="166" t="inlineStr">
+      <c r="A39" s="167" t="inlineStr">
         <is>
           <t>لا يوجد إجماع موثق</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="212" t="inlineStr">
+      <c r="A41" s="216" t="inlineStr">
         <is>
           <t>🟢 Upside &gt; +5%  =  فرصة رأسمالية   |   🟡 بين ±5%  =  تقييم عادل   |   🔴 Downside &gt; -5%  =  مكلف أو بلغ هدفه</t>
         </is>
@@ -10418,12 +10430,12 @@
           <t>الراجحي</t>
         </is>
       </c>
-      <c r="B3" s="213" t="inlineStr">
+      <c r="B3" s="217" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C3" s="154" t="inlineStr">
+      <c r="C3" s="155" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -10433,12 +10445,12 @@
           <t>18,000 ريال</t>
         </is>
       </c>
-      <c r="E3" s="214" t="inlineStr">
+      <c r="E3" s="218" t="inlineStr">
         <is>
           <t>نواة البنوك الإسلامية · توزيعات مستقرة · رؤية 2030</t>
         </is>
       </c>
-      <c r="F3" s="215" t="inlineStr">
+      <c r="F3" s="219" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10450,12 +10462,12 @@
           <t>STC</t>
         </is>
       </c>
-      <c r="B4" s="213" t="inlineStr">
+      <c r="B4" s="217" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C4" s="154" t="inlineStr">
+      <c r="C4" s="155" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -10465,12 +10477,12 @@
           <t>15,000 ريال</t>
         </is>
       </c>
-      <c r="E4" s="214" t="inlineStr">
+      <c r="E4" s="218" t="inlineStr">
         <is>
           <t>أعلى عائد توزيع · البنية الرقمية الوطنية</t>
         </is>
       </c>
-      <c r="F4" s="154" t="inlineStr">
+      <c r="F4" s="155" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
@@ -10482,12 +10494,12 @@
           <t>اكسترا</t>
         </is>
       </c>
-      <c r="B5" s="216" t="inlineStr">
+      <c r="B5" s="220" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C5" s="217" t="inlineStr">
+      <c r="C5" s="221" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10497,12 +10509,12 @@
           <t>12,000 ريال</t>
         </is>
       </c>
-      <c r="E5" s="218" t="inlineStr">
+      <c r="E5" s="222" t="inlineStr">
         <is>
           <t>قطاع التجزئة الدفاعي · توزيعات ممتازة · هامش أمان جيد</t>
         </is>
       </c>
-      <c r="F5" s="219" t="inlineStr">
+      <c r="F5" s="223" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10514,12 +10526,12 @@
           <t>المواساة</t>
         </is>
       </c>
-      <c r="B6" s="216" t="inlineStr">
+      <c r="B6" s="220" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C6" s="217" t="inlineStr">
+      <c r="C6" s="221" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10529,12 +10541,12 @@
           <t>10,000 ريال</t>
         </is>
       </c>
-      <c r="E6" s="218" t="inlineStr">
+      <c r="E6" s="222" t="inlineStr">
         <is>
           <t>رعاية صحية دفاعية · توزيع سنوي منتظم</t>
         </is>
       </c>
-      <c r="F6" s="217" t="inlineStr">
+      <c r="F6" s="221" t="inlineStr">
         <is>
           <t>منخفض</t>
         </is>
@@ -10546,12 +10558,12 @@
           <t>الإنماء</t>
         </is>
       </c>
-      <c r="B7" s="220" t="inlineStr">
+      <c r="B7" s="224" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C7" s="221" t="inlineStr">
+      <c r="C7" s="225" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10561,12 +10573,12 @@
           <t>10,000 ريال</t>
         </is>
       </c>
-      <c r="E7" s="222" t="inlineStr">
+      <c r="E7" s="226" t="inlineStr">
         <is>
           <t>أسرع البنوك نمواً · تراجع تقييم يوفر دخولاً جيدة</t>
         </is>
       </c>
-      <c r="F7" s="223" t="inlineStr">
+      <c r="F7" s="227" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10578,12 +10590,12 @@
           <t>سال</t>
         </is>
       </c>
-      <c r="B8" s="220" t="inlineStr">
+      <c r="B8" s="224" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C8" s="224" t="inlineStr">
+      <c r="C8" s="228" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -10593,12 +10605,12 @@
           <t>7,000 ريال</t>
         </is>
       </c>
-      <c r="E8" s="222" t="inlineStr">
+      <c r="E8" s="226" t="inlineStr">
         <is>
           <t>الاستفادة من نمو قطاع الخدمات اللوجستية الجوية</t>
         </is>
       </c>
-      <c r="F8" s="225" t="inlineStr">
+      <c r="F8" s="229" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -10610,12 +10622,12 @@
           <t>بنيان ريت</t>
         </is>
       </c>
-      <c r="B9" s="216" t="inlineStr">
+      <c r="B9" s="220" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C9" s="226" t="inlineStr">
+      <c r="C9" s="230" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -10625,12 +10637,12 @@
           <t>8,000 ريال</t>
         </is>
       </c>
-      <c r="E9" s="218" t="inlineStr">
+      <c r="E9" s="222" t="inlineStr">
         <is>
           <t>دخل إيجاري ثابت · عائد توزيع مرتفع · تنويع القطاعات</t>
         </is>
       </c>
-      <c r="F9" s="219" t="inlineStr">
+      <c r="F9" s="223" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
@@ -10642,12 +10654,12 @@
           <t>المتقدمة</t>
         </is>
       </c>
-      <c r="B10" s="213" t="inlineStr">
+      <c r="B10" s="217" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
-      <c r="C10" s="227" t="inlineStr">
+      <c r="C10" s="231" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -10657,83 +10669,83 @@
           <t>5,000 ريال</t>
         </is>
       </c>
-      <c r="E10" s="214" t="inlineStr">
+      <c r="E10" s="218" t="inlineStr">
         <is>
           <t>وزن محدود · مضاربة على العودة للربحية + رؤية 2030</t>
         </is>
       </c>
-      <c r="F10" s="228" t="inlineStr">
+      <c r="F10" s="232" t="inlineStr">
         <is>
           <t>مرتفع</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="229" t="inlineStr">
+      <c r="A11" s="233" t="inlineStr">
         <is>
           <t>بدجت</t>
         </is>
       </c>
-      <c r="B11" s="230" t="inlineStr">
+      <c r="B11" s="234" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C11" s="231" t="inlineStr">
+      <c r="C11" s="235" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" s="232" t="inlineStr">
+      <c r="D11" s="236" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="233" t="inlineStr">
+      <c r="E11" s="237" t="inlineStr">
         <is>
           <t>⚠ تأجيل حتى توضيح أسباب تراجع Q1 2026</t>
         </is>
       </c>
-      <c r="F11" s="234" t="inlineStr">
+      <c r="F11" s="238" t="inlineStr">
         <is>
           <t>متوسط-مرتفع</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="235" t="inlineStr">
+      <c r="A12" s="239" t="inlineStr">
         <is>
           <t>كاش</t>
         </is>
       </c>
-      <c r="B12" s="236" t="inlineStr">
+      <c r="B12" s="240" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C12" s="237" t="inlineStr">
+      <c r="C12" s="241" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D12" s="238" t="inlineStr">
+      <c r="D12" s="242" t="inlineStr">
         <is>
           <t>15,000 ريال</t>
         </is>
       </c>
-      <c r="E12" s="239" t="inlineStr">
+      <c r="E12" s="243" t="inlineStr">
         <is>
           <t>احتياطي للشراء عند الانخفاض · الحد الأدنى المقترح</t>
         </is>
       </c>
-      <c r="F12" s="240" t="inlineStr">
+      <c r="F12" s="244" t="inlineStr">
         <is>
           <t>صفر</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="241" t="inlineStr">
+      <c r="A14" s="245" t="inlineStr">
         <is>
           <t>استراتيجية الشراء التدريجي (Staggered Entry):
 • المرحلة 1 (الآن): الراجحي + STC + اكسترا + المواساة = 55% من المحفظة (على دفعتين)
@@ -10784,132 +10796,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
-        <v>66.59999999999999</v>
+      <c r="B3" s="248" t="n">
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
-        <v>40000</v>
+      <c r="B4" s="250" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
-        <v>4000</v>
+      <c r="B5" s="248" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>2.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>20.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Blend</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -10936,80 +10948,80 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>23500</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>30100</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>29800</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>34200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>14979</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>17151</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>16621</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>19722</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>12000</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>16000</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>14500</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>18500</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تمويل مشاريع عملاقة + صيرفة إسلامية + تمويل الأفراد + رقمنة الخدمات</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: متطلبات كفاية رأس المال (SAMA) · تأثير المنح على المعدلات للسهم · تنافسية ضيقة</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
-        <is>
-          <t>⚠ تنبيه: ✅ سعر مُعدَّل بعد المنح (1 سهم / 2) → الأسهم ارتفعت من 4B إلى 6B</t>
+      <c r="A22" s="257" t="inlineStr">
+        <is>
+          <t>⚠ تنبيه: ✅ بعد منح الأسهم (1 سهم مجاني لكل 2) → الأسهم أصبحت 6B سهم | سعر مُعدَّل</t>
         </is>
       </c>
     </row>
@@ -11050,132 +11062,132 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="242" t="inlineStr">
+      <c r="A2" s="246" t="inlineStr">
         <is>
           <t>المؤشر</t>
         </is>
       </c>
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="246" t="inlineStr">
         <is>
           <t>القيمة</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="243" t="inlineStr">
+      <c r="A3" s="247" t="inlineStr">
         <is>
           <t>السعر الحالي (ريال)</t>
         </is>
       </c>
-      <c r="B3" s="244" t="n">
-        <v>23.53</v>
+      <c r="B3" s="248" t="n">
+        <v>23.86</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245" t="inlineStr">
+      <c r="A4" s="249" t="inlineStr">
         <is>
           <t>رأس المال (م.ريال)</t>
         </is>
       </c>
-      <c r="B4" s="246" t="n">
+      <c r="B4" s="250" t="n">
         <v>19922</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="243" t="inlineStr">
+      <c r="A5" s="247" t="inlineStr">
         <is>
           <t>عدد الأسهم (م.سهم)</t>
         </is>
       </c>
-      <c r="B5" s="244" t="n">
+      <c r="B5" s="248" t="n">
         <v>1992</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="245" t="inlineStr">
+      <c r="A6" s="249" t="inlineStr">
         <is>
           <t>مضاعف الربحية (P/E)</t>
         </is>
       </c>
-      <c r="B6" s="246" t="n">
+      <c r="B6" s="250" t="n">
         <v>9.4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="243" t="inlineStr">
+      <c r="A7" s="247" t="inlineStr">
         <is>
           <t>مضاعف الدفتري (P/B)</t>
         </is>
       </c>
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="248" t="n">
         <v>1.86</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="245" t="inlineStr">
+      <c r="A8" s="249" t="inlineStr">
         <is>
           <t>عائد التوزيع %</t>
         </is>
       </c>
-      <c r="B8" s="246" t="n">
+      <c r="B8" s="250" t="n">
         <v>4.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="243" t="inlineStr">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>العائد على حقوق المساهمين %</t>
         </is>
       </c>
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="248" t="n">
         <v>21.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="245" t="inlineStr">
+      <c r="A10" s="249" t="inlineStr">
         <is>
           <t>تصنيف المحفظة</t>
         </is>
       </c>
-      <c r="B10" s="246" t="inlineStr">
+      <c r="B10" s="250" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="243" t="inlineStr">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>مستوى المخاطرة</t>
         </is>
       </c>
-      <c r="B11" s="244" t="inlineStr">
+      <c r="B11" s="248" t="inlineStr">
         <is>
           <t>منخفض-متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="245" t="inlineStr">
+      <c r="A12" s="249" t="inlineStr">
         <is>
           <t>التوصية</t>
         </is>
       </c>
-      <c r="B12" s="246" t="inlineStr">
+      <c r="B12" s="250" t="inlineStr">
         <is>
           <t>تراكم</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="247" t="inlineStr">
+      <c r="A14" s="251" t="inlineStr">
         <is>
           <t>الأداء المالي التاريخي (مليون ريال)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="248" t="inlineStr">
+      <c r="A15" s="252" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
@@ -11202,78 +11214,78 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="249" t="inlineStr">
+      <c r="A16" s="253" t="inlineStr">
         <is>
           <t>الإيرادات</t>
         </is>
       </c>
-      <c r="B16" s="250" t="n">
+      <c r="B16" s="254" t="n">
         <v>5500</v>
       </c>
-      <c r="C16" s="250" t="n">
+      <c r="C16" s="254" t="n">
         <v>7200</v>
       </c>
-      <c r="D16" s="250" t="n">
+      <c r="D16" s="254" t="n">
         <v>8700</v>
       </c>
-      <c r="E16" s="250" t="n">
+      <c r="E16" s="254" t="n">
         <v>10200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="249" t="inlineStr">
+      <c r="A17" s="253" t="inlineStr">
         <is>
           <t>صافي الربح</t>
         </is>
       </c>
-      <c r="B17" s="250" t="n">
+      <c r="B17" s="254" t="n">
         <v>2714</v>
       </c>
-      <c r="C17" s="250" t="n">
+      <c r="C17" s="254" t="n">
         <v>3599</v>
       </c>
-      <c r="D17" s="250" t="n">
+      <c r="D17" s="254" t="n">
         <v>4839</v>
       </c>
-      <c r="E17" s="250" t="n">
+      <c r="E17" s="254" t="n">
         <v>5832</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="249" t="inlineStr">
+      <c r="A18" s="253" t="inlineStr">
         <is>
           <t>التدفق النقدي التشغيلي</t>
         </is>
       </c>
-      <c r="B18" s="250" t="n">
+      <c r="B18" s="254" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="250" t="n">
+      <c r="C18" s="254" t="n">
         <v>4200</v>
       </c>
-      <c r="D18" s="250" t="n">
+      <c r="D18" s="254" t="n">
         <v>5500</v>
       </c>
-      <c r="E18" s="250" t="n">
+      <c r="E18" s="254" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="251" t="inlineStr">
+      <c r="A20" s="255" t="inlineStr">
         <is>
           <t>رؤية 2030 والمحفزات: تمويل المشاريع الكبرى + تمويل الرهن العقاري + SME Lending + رقمنة</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="252" t="inlineStr">
+      <c r="A21" s="256" t="inlineStr">
         <is>
           <t>المخاطر: بنك أصغر نسبياً · انكشاف عقاري · سيولة تداول أقل</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="253" t="inlineStr">
+      <c r="A22" s="257" t="inlineStr">
         <is>
           <t>⚠ تنبيه: تحول إلى توزيعات ربعية منذ 2023</t>
         </is>

--- a/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
+++ b/saudi-investment-analysis/Saudi_Portfolio_Analysis_2026.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="49">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +170,12 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00888888"/>
       <sz val="9"/>
     </font>
     <font>
@@ -852,7 +858,7 @@
     <xf numFmtId="3" fontId="15" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="17" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -861,7 +867,7 @@
     <xf numFmtId="3" fontId="15" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="17" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -870,28 +876,28 @@
     <xf numFmtId="3" fontId="15" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="17" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="30" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="32" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="22" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="23" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -921,7 +927,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -933,25 +939,25 @@
     <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="27" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -963,25 +969,25 @@
     <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -993,19 +999,19 @@
     <xf numFmtId="167" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="27" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1017,22 +1023,22 @@
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="27" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="27" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1044,22 +1050,22 @@
     <xf numFmtId="167" fontId="4" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="27" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="28" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="27" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1071,52 +1077,52 @@
     <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="24" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1128,22 +1134,22 @@
     <xf numFmtId="167" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1152,220 +1158,220 @@
     <xf numFmtId="0" fontId="3" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="34" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="34" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="36" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="37" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="34" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="37" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="36" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="34" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="24" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="34" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="33" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="34" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="36" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="37" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="37" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="38" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1374,16 +1380,16 @@
     <xf numFmtId="0" fontId="12" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1392,10 +1398,10 @@
     <xf numFmtId="0" fontId="12" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="48" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="48" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1423,7 +1429,7 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7892,7 +7898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7973,15 +7979,13 @@
       <c r="E4" s="71" t="n">
         <v>34200</v>
       </c>
-      <c r="F4" s="72" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="G4" s="72" t="inlineStr">
-        <is>
-          <t>+14.8%</t>
-        </is>
+      <c r="F4" s="72">
+        <f>IFERROR((E4/B4)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G4" s="72">
+        <f>IFERROR((E4-D4)/ABS(D4),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -8002,15 +8006,13 @@
       <c r="E5" s="74" t="n">
         <v>19722</v>
       </c>
-      <c r="F5" s="75" t="inlineStr">
-        <is>
-          <t>9.6%</t>
-        </is>
-      </c>
-      <c r="G5" s="75" t="inlineStr">
-        <is>
-          <t>+18.7%</t>
-        </is>
+      <c r="F5" s="75">
+        <f>IFERROR((E5/B5)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G5" s="75">
+        <f>IFERROR((E5-D5)/ABS(D5),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -8031,15 +8033,13 @@
       <c r="E6" s="77" t="n">
         <v>18500</v>
       </c>
-      <c r="F6" s="78" t="inlineStr">
-        <is>
-          <t>15.5%</t>
-        </is>
-      </c>
-      <c r="G6" s="78" t="inlineStr">
-        <is>
-          <t>+27.6%</t>
-        </is>
+      <c r="F6" s="78">
+        <f>IFERROR((E6/B6)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G6" s="78">
+        <f>IFERROR((E6-D6)/ABS(D6),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -8060,15 +8060,13 @@
       <c r="E7" s="77" t="n">
         <v>100185</v>
       </c>
-      <c r="F7" s="78" t="inlineStr">
-        <is>
-          <t>17.3%</t>
-        </is>
-      </c>
-      <c r="G7" s="78" t="inlineStr">
-        <is>
-          <t>+11.0%</t>
-        </is>
+      <c r="F7" s="78">
+        <f>IFERROR((E7/B7)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G7" s="78">
+        <f>IFERROR((E7-D7)/ABS(D7),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -8133,15 +8131,13 @@
       <c r="E11" s="71" t="n">
         <v>10200</v>
       </c>
-      <c r="F11" s="72" t="inlineStr">
-        <is>
-          <t>22.9%</t>
-        </is>
-      </c>
-      <c r="G11" s="72" t="inlineStr">
-        <is>
-          <t>+17.2%</t>
-        </is>
+      <c r="F11" s="72">
+        <f>IFERROR((E11/B11)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G11" s="72">
+        <f>IFERROR((E11-D11)/ABS(D11),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -8162,15 +8158,13 @@
       <c r="E12" s="74" t="n">
         <v>5832</v>
       </c>
-      <c r="F12" s="75" t="inlineStr">
-        <is>
-          <t>29.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="75" t="inlineStr">
-        <is>
-          <t>+20.5%</t>
-        </is>
+      <c r="F12" s="75">
+        <f>IFERROR((E12/B12)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G12" s="75">
+        <f>IFERROR((E12-D12)/ABS(D12),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -8191,15 +8185,13 @@
       <c r="E13" s="77" t="n">
         <v>6800</v>
       </c>
-      <c r="F13" s="78" t="inlineStr">
-        <is>
-          <t>31.4%</t>
-        </is>
-      </c>
-      <c r="G13" s="78" t="inlineStr">
-        <is>
-          <t>+23.6%</t>
-        </is>
+      <c r="F13" s="78">
+        <f>IFERROR((E13/B13)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G13" s="78">
+        <f>IFERROR((E13-D13)/ABS(D13),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -8220,15 +8212,13 @@
       <c r="E14" s="77" t="n">
         <v>29500</v>
       </c>
-      <c r="F14" s="78" t="inlineStr">
-        <is>
-          <t>17.9%</t>
-        </is>
-      </c>
-      <c r="G14" s="78" t="inlineStr">
-        <is>
-          <t>+18.0%</t>
-        </is>
+      <c r="F14" s="78">
+        <f>IFERROR((E14/B14)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G14" s="78">
+        <f>IFERROR((E14-D14)/ABS(D14),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8293,15 +8283,13 @@
       <c r="E18" s="71" t="n">
         <v>75893</v>
       </c>
-      <c r="F18" s="72" t="inlineStr">
-        <is>
-          <t>6.4%</t>
-        </is>
-      </c>
-      <c r="G18" s="72" t="inlineStr">
-        <is>
-          <t>+5.7%</t>
-        </is>
+      <c r="F18" s="72">
+        <f>IFERROR((E18/B18)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G18" s="72">
+        <f>IFERROR((E18-D18)/ABS(D18),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -8322,15 +8310,13 @@
       <c r="E19" s="74" t="n">
         <v>24689</v>
       </c>
-      <c r="F19" s="75" t="inlineStr">
-        <is>
-          <t>30.5%</t>
-        </is>
-      </c>
-      <c r="G19" s="75" t="inlineStr">
-        <is>
-          <t>+85.6%</t>
-        </is>
+      <c r="F19" s="75">
+        <f>IFERROR((E19/B19)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G19" s="75">
+        <f>IFERROR((E19-D19)/ABS(D19),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -8351,15 +8337,13 @@
       <c r="E20" s="77" t="n">
         <v>24500</v>
       </c>
-      <c r="F20" s="78" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
-      <c r="G20" s="78" t="inlineStr">
-        <is>
-          <t>+11.4%</t>
-        </is>
+      <c r="F20" s="78">
+        <f>IFERROR((E20/B20)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G20" s="78">
+        <f>IFERROR((E20-D20)/ABS(D20),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -8380,15 +8364,13 @@
       <c r="E21" s="77" t="n">
         <v>55000</v>
       </c>
-      <c r="F21" s="79" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="G21" s="78" t="inlineStr">
-        <is>
-          <t>+14.6%</t>
-        </is>
+      <c r="F21" s="79">
+        <f>IFERROR((E21/B21)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G21" s="78">
+        <f>IFERROR((E21-D21)/ABS(D21),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8453,15 +8435,13 @@
       <c r="E25" s="71" t="n">
         <v>1630</v>
       </c>
-      <c r="F25" s="72" t="inlineStr">
-        <is>
-          <t>21.9%</t>
-        </is>
-      </c>
-      <c r="G25" s="72" t="inlineStr">
-        <is>
-          <t>+12.3%</t>
-        </is>
+      <c r="F25" s="72">
+        <f>IFERROR((E25/B25)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G25" s="72">
+        <f>IFERROR((E25-D25)/ABS(D25),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -8482,15 +8462,13 @@
       <c r="E26" s="74" t="n">
         <v>661</v>
       </c>
-      <c r="F26" s="75" t="inlineStr">
-        <is>
-          <t>27.4%</t>
-        </is>
-      </c>
-      <c r="G26" s="75" t="inlineStr">
-        <is>
-          <t>+29.4%</t>
-        </is>
+      <c r="F26" s="75">
+        <f>IFERROR((E26/B26)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G26" s="75">
+        <f>IFERROR((E26-D26)/ABS(D26),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -8511,15 +8489,13 @@
       <c r="E27" s="77" t="n">
         <v>820</v>
       </c>
-      <c r="F27" s="78" t="inlineStr">
-        <is>
-          <t>27.0%</t>
-        </is>
-      </c>
-      <c r="G27" s="78" t="inlineStr">
-        <is>
-          <t>+20.6%</t>
-        </is>
+      <c r="F27" s="78">
+        <f>IFERROR((E27/B27)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G27" s="78">
+        <f>IFERROR((E27-D27)/ABS(D27),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -8540,15 +8516,13 @@
       <c r="E28" s="77" t="n">
         <v>2300</v>
       </c>
-      <c r="F28" s="78" t="inlineStr">
-        <is>
-          <t>24.2%</t>
-        </is>
-      </c>
-      <c r="G28" s="78" t="inlineStr">
-        <is>
-          <t>+21.1%</t>
-        </is>
+      <c r="F28" s="78">
+        <f>IFERROR((E28/B28)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G28" s="78">
+        <f>IFERROR((E28-D28)/ABS(D28),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -8613,15 +8587,13 @@
       <c r="E32" s="71" t="n">
         <v>2879</v>
       </c>
-      <c r="F32" s="72" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="G32" s="72" t="inlineStr">
-        <is>
-          <t>+6.4%</t>
-        </is>
+      <c r="F32" s="72">
+        <f>IFERROR((E32/B32)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G32" s="72">
+        <f>IFERROR((E32-D32)/ABS(D32),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -8642,15 +8614,13 @@
       <c r="E33" s="74" t="n">
         <v>646</v>
       </c>
-      <c r="F33" s="75" t="inlineStr">
-        <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="G33" s="80" t="inlineStr">
-        <is>
-          <t>-1.8%</t>
-        </is>
+      <c r="F33" s="75">
+        <f>IFERROR((E33/B33)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G33" s="80">
+        <f>IFERROR((E33-D33)/ABS(D33),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -8671,15 +8641,13 @@
       <c r="E34" s="77" t="n">
         <v>780</v>
       </c>
-      <c r="F34" s="78" t="inlineStr">
-        <is>
-          <t>6.3%</t>
-        </is>
-      </c>
-      <c r="G34" s="81" t="inlineStr">
-        <is>
-          <t>-2.5%</t>
-        </is>
+      <c r="F34" s="78">
+        <f>IFERROR((E34/B34)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G34" s="81">
+        <f>IFERROR((E34-D34)/ABS(D34),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -8700,15 +8668,13 @@
       <c r="E35" s="77" t="n">
         <v>4000</v>
       </c>
-      <c r="F35" s="78" t="inlineStr">
-        <is>
-          <t>12.6%</t>
-        </is>
-      </c>
-      <c r="G35" s="78" t="inlineStr">
-        <is>
-          <t>+11.1%</t>
-        </is>
+      <c r="F35" s="78">
+        <f>IFERROR((E35/B35)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G35" s="78">
+        <f>IFERROR((E35-D35)/ABS(D35),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -8773,15 +8739,13 @@
       <c r="E39" s="71" t="n">
         <v>1980</v>
       </c>
-      <c r="F39" s="72" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="G39" s="72" t="inlineStr">
-        <is>
-          <t>+13.1%</t>
-        </is>
+      <c r="F39" s="72">
+        <f>IFERROR((E39/B39)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G39" s="72">
+        <f>IFERROR((E39-D39)/ABS(D39),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -8802,15 +8766,13 @@
       <c r="E40" s="74" t="n">
         <v>312</v>
       </c>
-      <c r="F40" s="75" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="G40" s="75" t="inlineStr">
-        <is>
-          <t>+12.6%</t>
-        </is>
+      <c r="F40" s="75">
+        <f>IFERROR((E40/B40)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G40" s="75">
+        <f>IFERROR((E40-D40)/ABS(D40),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -8831,15 +8793,13 @@
       <c r="E41" s="77" t="n">
         <v>550</v>
       </c>
-      <c r="F41" s="78" t="inlineStr">
-        <is>
-          <t>13.1%</t>
-        </is>
-      </c>
-      <c r="G41" s="78" t="inlineStr">
-        <is>
-          <t>+7.8%</t>
-        </is>
+      <c r="F41" s="78">
+        <f>IFERROR((E41/B41)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G41" s="78">
+        <f>IFERROR((E41-D41)/ABS(D41),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -8860,15 +8820,13 @@
       <c r="E42" s="77" t="n">
         <v>1903</v>
       </c>
-      <c r="F42" s="78" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="G42" s="78" t="inlineStr">
-        <is>
-          <t>+10.3%</t>
-        </is>
+      <c r="F42" s="78">
+        <f>IFERROR((E42/B42)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G42" s="78">
+        <f>IFERROR((E42-D42)/ABS(D42),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -8933,15 +8891,13 @@
       <c r="E46" s="71" t="n">
         <v>6781</v>
       </c>
-      <c r="F46" s="72" t="inlineStr">
-        <is>
-          <t>14.6%</t>
-        </is>
-      </c>
-      <c r="G46" s="72" t="inlineStr">
-        <is>
-          <t>+16.9%</t>
-        </is>
+      <c r="F46" s="72">
+        <f>IFERROR((E46/B46)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G46" s="72">
+        <f>IFERROR((E46-D46)/ABS(D46),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -8962,15 +8918,13 @@
       <c r="E47" s="74" t="n">
         <v>534</v>
       </c>
-      <c r="F47" s="75" t="inlineStr">
-        <is>
-          <t>24.0%</t>
-        </is>
-      </c>
-      <c r="G47" s="75" t="inlineStr">
-        <is>
-          <t>+36.9%</t>
-        </is>
+      <c r="F47" s="75">
+        <f>IFERROR((E47/B47)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G47" s="75">
+        <f>IFERROR((E47-D47)/ABS(D47),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -8991,15 +8945,13 @@
       <c r="E48" s="77" t="n">
         <v>620</v>
       </c>
-      <c r="F48" s="78" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="G48" s="78" t="inlineStr">
-        <is>
-          <t>+24.0%</t>
-        </is>
+      <c r="F48" s="78">
+        <f>IFERROR((E48/B48)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G48" s="78">
+        <f>IFERROR((E48-D48)/ABS(D48),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -9020,15 +8972,13 @@
       <c r="E49" s="77" t="n">
         <v>1900</v>
       </c>
-      <c r="F49" s="78" t="inlineStr">
-        <is>
-          <t>16.6%</t>
-        </is>
-      </c>
-      <c r="G49" s="78" t="inlineStr">
-        <is>
-          <t>+15.2%</t>
-        </is>
+      <c r="F49" s="78">
+        <f>IFERROR((E49/B49)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G49" s="78">
+        <f>IFERROR((E49-D49)/ABS(D49),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -9093,15 +9043,13 @@
       <c r="E53" s="71" t="n">
         <v>1700</v>
       </c>
-      <c r="F53" s="82" t="inlineStr">
-        <is>
-          <t>-6.8%</t>
-        </is>
-      </c>
-      <c r="G53" s="82" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
+      <c r="F53" s="82">
+        <f>IFERROR((E53/B53)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G53" s="82">
+        <f>IFERROR((E53-D53)/ABS(D53),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -9122,15 +9070,13 @@
       <c r="E54" s="83" t="n">
         <v>-259</v>
       </c>
-      <c r="F54" s="84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G54" s="80" t="inlineStr">
-        <is>
-          <t>-404.7%</t>
-        </is>
+      <c r="F54" s="84">
+        <f>IFERROR((E54/B54)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G54" s="80">
+        <f>IFERROR((E54-D54)/ABS(D54),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -9151,15 +9097,13 @@
       <c r="E55" s="77" t="n">
         <v>50</v>
       </c>
-      <c r="F55" s="81" t="inlineStr">
-        <is>
-          <t>-51.9%</t>
-        </is>
-      </c>
-      <c r="G55" s="81" t="inlineStr">
-        <is>
-          <t>-72.2%</t>
-        </is>
+      <c r="F55" s="81">
+        <f>IFERROR((E55/B55)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G55" s="81">
+        <f>IFERROR((E55-D55)/ABS(D55),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -9180,15 +9124,13 @@
       <c r="E56" s="77" t="n">
         <v>2000</v>
       </c>
-      <c r="F56" s="81" t="inlineStr">
-        <is>
-          <t>-3.1%</t>
-        </is>
-      </c>
-      <c r="G56" s="81" t="inlineStr">
-        <is>
-          <t>-13.0%</t>
-        </is>
+      <c r="F56" s="81">
+        <f>IFERROR((E56/B56)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G56" s="81">
+        <f>IFERROR((E56-D56)/ABS(D56),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -9253,15 +9195,13 @@
       <c r="E60" s="71" t="n">
         <v>190</v>
       </c>
-      <c r="F60" s="72" t="inlineStr">
-        <is>
-          <t>10.7%</t>
-        </is>
-      </c>
-      <c r="G60" s="72" t="inlineStr">
-        <is>
-          <t>+11.8%</t>
-        </is>
+      <c r="F60" s="72">
+        <f>IFERROR((E60/B60)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G60" s="72">
+        <f>IFERROR((E60-D60)/ABS(D60),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -9282,15 +9222,13 @@
       <c r="E61" s="74" t="n">
         <v>118</v>
       </c>
-      <c r="F61" s="75" t="inlineStr">
-        <is>
-          <t>11.6%</t>
-        </is>
-      </c>
-      <c r="G61" s="75" t="inlineStr">
-        <is>
-          <t>+12.4%</t>
-        </is>
+      <c r="F61" s="75">
+        <f>IFERROR((E61/B61)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G61" s="75">
+        <f>IFERROR((E61-D61)/ABS(D61),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -9311,15 +9249,13 @@
       <c r="E62" s="77" t="n">
         <v>130</v>
       </c>
-      <c r="F62" s="78" t="inlineStr">
-        <is>
-          <t>13.0%</t>
-        </is>
-      </c>
-      <c r="G62" s="78" t="inlineStr">
-        <is>
-          <t>+13.0%</t>
-        </is>
+      <c r="F62" s="78">
+        <f>IFERROR((E62/B62)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G62" s="78">
+        <f>IFERROR((E62-D62)/ABS(D62),"N/A")</f>
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -9340,28 +9276,147 @@
       <c r="E63" s="77" t="n">
         <v>1610</v>
       </c>
-      <c r="F63" s="79" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="G63" s="78" t="inlineStr">
-        <is>
-          <t>+1.3%</t>
+      <c r="F63" s="79">
+        <f>IFERROR((E63/B63)^(1/3)-1,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G63" s="78">
+        <f>IFERROR((E63-D63)/ABS(D63),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="47" t="inlineStr">
+        <is>
+          <t>📖  مسرد المصطلحات والاختصارات المستخدمة في هذه الورقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="48" t="inlineStr">
+        <is>
+          <t>المصطلح / الاختصار</t>
+        </is>
+      </c>
+      <c r="E68" s="48" t="inlineStr">
+        <is>
+          <t>الشرح والصيغة</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="49" t="inlineStr">
+        <is>
+          <t>CAGR 3Y — معدل النمو السنوي المركب</t>
+        </is>
+      </c>
+      <c r="E69" s="50" t="inlineStr">
+        <is>
+          <t>الصيغة: (قيمة 2024 ÷ قيمة 2021)^(1/3) − 1  |  يقيس متوسط النمو السنوي على 3 سنوات</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="51" t="inlineStr">
+        <is>
+          <t>نمو 2024/2023 — YoY</t>
+        </is>
+      </c>
+      <c r="E70" s="52" t="inlineStr">
+        <is>
+          <t>الصيغة: (2024 − 2023) ÷ |2023|  |  التغيير السنوي المقارن</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="49" t="inlineStr">
+        <is>
+          <t>الإيرادات</t>
+        </is>
+      </c>
+      <c r="E71" s="50" t="inlineStr">
+        <is>
+          <t>إجمالي الدخل التشغيلي (المبيعات / العائد على التمويل للبنوك)  |  م. ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="51" t="inlineStr">
+        <is>
+          <t>صافي الربح</t>
+        </is>
+      </c>
+      <c r="E72" s="52" t="inlineStr">
+        <is>
+          <t>الأرباح بعد خصم جميع التكاليف والضرائب  |  م. ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="49" t="inlineStr">
+        <is>
+          <t>OCF — التدفق النقدي التشغيلي</t>
+        </is>
+      </c>
+      <c r="E73" s="50" t="inlineStr">
+        <is>
+          <t>النقد الفعلي المتولد من العمليات (أقل تأثراً بالسياسات المحاسبية من الربح)  |  م. ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="51" t="inlineStr">
+        <is>
+          <t>حقوق المساهمين</t>
+        </is>
+      </c>
+      <c r="E74" s="52" t="inlineStr">
+        <is>
+          <t>إجمالي الأصول − إجمالي الالتزامات  |  القيمة الدفترية للشركة  |  م. ريال</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="49" t="inlineStr">
+        <is>
+          <t>م. = مليون ريال</t>
+        </is>
+      </c>
+      <c r="E75" s="50" t="inlineStr">
+        <is>
+          <t>وحدة قياس جميع الأرقام في هذه الورقة</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="27">
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E72:G72"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E75:G75"/>
     <mergeCell ref="A16:G16"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A74:D74"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9374,7 +9429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9947,11 +10002,174 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>📖  مسرد المصطلحات والاختصارات المستخدمة في هذه الورقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>المصطلح / الاختصار</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="inlineStr">
+        <is>
+          <t>الشرح والصيغة</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>P/E — مكرر الربحية</t>
+        </is>
+      </c>
+      <c r="E19" s="50" t="inlineStr">
+        <is>
+          <t>السعر ÷ EPS  |  القيمة العادلة = متوسط P/E القطاعي × EPS 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>P/B — مكرر القيمة الدفترية</t>
+        </is>
+      </c>
+      <c r="E20" s="52" t="inlineStr">
+        <is>
+          <t>(سعر × أسهم) ÷ حقوق الملكية  |  القيمة العادلة = متوسط P/B القطاعي × القيمة الدفترية للسهم</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>DDM — نموذج خصم التوزيعات</t>
+        </is>
+      </c>
+      <c r="E21" s="50" t="inlineStr">
+        <is>
+          <t>DPS₁ ÷ (WACC − g)  |  Gordon Growth Model  |  مناسب لشركات التوزيع المنتظم</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="51" t="inlineStr">
+        <is>
+          <t>DCF — التدفقات النقدية المخصومة</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>Σ FCF÷(1+WACC)^t + Terminal Value  |  5 سنوات + قيمة نهائية  |  g_terminal = 3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="E23" s="50" t="inlineStr">
+        <is>
+          <t>قيمة المنشأة ÷ EBITDA  |  مضاعف القطاع × OCF (كـProxy للـEBITDA) ÷ الأسهم</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>P/E ÷ معدل نمو EPS%  |  PEG &lt; 1 يشير لتقييم مغرٍ نسبياً  |  لا ينطبق عند الخسارة</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>P/S — السعر إلى الإيرادات</t>
+        </is>
+      </c>
+      <c r="E25" s="50" t="inlineStr">
+        <is>
+          <t>(سعر × أسهم) ÷ الإيرادات  |  مفيد لتقييم شركات النمو أو عند غياب الربحية</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="51" t="inlineStr">
+        <is>
+          <t>هامش الأمان%</t>
+        </is>
+      </c>
+      <c r="E26" s="52" t="inlineStr">
+        <is>
+          <t>(متوسط القيمة العادلة − السعر) ÷ السعر × 100  |  🟢 موجب = هامش أمان  |  🔴 سالب = علاوة سعرية</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>WACC — تكلفة رأس المال</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>متوسط تكلفة رأس المال المرجح  |  معدل الخصم في نموذج DCF  |  يتفاوت بين 8.5% - 13% حسب القطاع</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>إجماع المحللين</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>متوسط أسعار مستهدفة من بيوت خبرة متعددة  |  للتفاصيل: راجع ورقة بيوت الخبرة</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="26">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E27:N27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E26:N26"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E25:N25"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="E22:N22"/>
+    <mergeCell ref="E18:N18"/>
+    <mergeCell ref="E21:N21"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:N24"/>
+    <mergeCell ref="E23:N23"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E20:N20"/>
     <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="E28:N28"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="E19:N19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9963,7 +10181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10811,20 +11029,127 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="47" t="inlineStr">
+        <is>
+          <t>📖  مسرد المصطلحات والاختصارات المستخدمة في هذه الورقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>المصطلح / الاختصار</t>
+        </is>
+      </c>
+      <c r="E45" s="48" t="inlineStr">
+        <is>
+          <t>الشرح والصيغة</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t>السعر المستهدف</t>
+        </is>
+      </c>
+      <c r="E46" s="50" t="inlineStr">
+        <is>
+          <t>تقدير المحلل للقيمة العادلة للسهم خلال 12 شهراً القادمة  |  بالريال السعودي</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>Upside% — الارتفاع المتوقع</t>
+        </is>
+      </c>
+      <c r="E47" s="52" t="inlineStr">
+        <is>
+          <t>(السعر المستهدف − السعر الحالي) ÷ السعر الحالي × 100  |  🟢 موجب = فرصة  |  🔴 سالب = مبالغ في قيمته</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="49" t="inlineStr">
+        <is>
+          <t>OW — Overweight (زيادة المراكز)</t>
+        </is>
+      </c>
+      <c r="E48" s="50" t="inlineStr">
+        <is>
+          <t>توصية بوزن أعلى من المعيار المرجعي — تعادل Buy/Strong Buy في التصنيفات الأخرى</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>Neutral — محايد</t>
+        </is>
+      </c>
+      <c r="E49" s="52" t="inlineStr">
+        <is>
+          <t>الإبقاء على المراكز الحالية دون زيادة أو تخفيض  |  تعادل Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>إجماع (Consensus)</t>
+        </is>
+      </c>
+      <c r="E50" s="50" t="inlineStr">
+        <is>
+          <t>متوسط أسعار مستهدفة ومتوسط التوصيات من عدة بيوت خبرة</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>مصدر البيانات</t>
+        </is>
+      </c>
+      <c r="E51" s="52" t="inlineStr">
+        <is>
+          <t>Investing.com / Bloomberg / الجزيرة كابيتال / مورغان ستانلي  |  مايو 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E50:G50"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="E51:G51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10836,7 +11161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11224,10 +11549,131 @@
     <row r="17" ht="20" customHeight="1"/>
     <row r="18" ht="20" customHeight="1"/>
     <row r="19" ht="20" customHeight="1"/>
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>📖  مسرد المصطلحات والاختصارات المستخدمة في هذه الورقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>المصطلح / الاختصار</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>الشرح والصيغة</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>الوزن المقترح%</t>
+        </is>
+      </c>
+      <c r="E25" s="50" t="inlineStr">
+        <is>
+          <t>نسبة تخصيص الاستثمار في كل ورقة مالية من إجمالي قيمة المحفظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="51" t="inlineStr">
+        <is>
+          <t>مبلغ مقترح (100K)</t>
+        </is>
+      </c>
+      <c r="E26" s="52" t="inlineStr">
+        <is>
+          <t>التوزيع بالريال لمحفظة افتراضية قيمتها 100,000 ريال  |  يُعدَّل تناسبياً لأي قيمة أخرى</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>🟢 Value</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="inlineStr">
+        <is>
+          <t>شركة قيمة — تُتداول بأقل من قيمتها الجوهرية — تناسب المستثمر المحافظ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>🔵 Growth</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>شركة نمو — توسع مرتفع وأرباح متصاعدة — تناسب المستثمر طويل المدى</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>🟡 Blend</t>
+        </is>
+      </c>
+      <c r="E29" s="50" t="inlineStr">
+        <is>
+          <t>مزيج قيمة ونمو — توازن بين الاستقرار والنمو</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>كاش</t>
+        </is>
+      </c>
+      <c r="E30" s="52" t="inlineStr">
+        <is>
+          <t>سيولة احتياطية لاستغلال فرص الشراء عند تراجعات السوق</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>مستوى المخاطرة</t>
+        </is>
+      </c>
+      <c r="E31" s="50" t="inlineStr">
+        <is>
+          <t>تقدير نوعي: منخفض / منخفض-متوسط / متوسط / متوسط-مرتفع / مرتفع</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="19">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="A14:H19"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
